--- a/assignment/normalization_examples/Normalisation.xlsx
+++ b/assignment/normalization_examples/Normalisation.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10811"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/connor.3.robinson@bt.com/Documents/Repos/relational-db/assignment/normalization_examples/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/connorrobinson/Documents/Repos/Relational-Databases/assignment/normalization_examples/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F7CD8232-C04A-4147-91D9-8697284567A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DD11A4E-E2F3-8647-B19A-4A234C68F882}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="34560" windowHeight="21600" activeTab="1" xr2:uid="{4F075678-4195-7143-B183-D28923453708}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20040" activeTab="4" xr2:uid="{4F075678-4195-7143-B183-D28923453708}"/>
   </bookViews>
   <sheets>
     <sheet name="0NF" sheetId="1" r:id="rId1"/>
     <sheet name="1NF" sheetId="2" r:id="rId2"/>
+    <sheet name="0NF 2.0" sheetId="3" r:id="rId3"/>
+    <sheet name="1NF 2.0" sheetId="4" r:id="rId4"/>
+    <sheet name="BCNF" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -37,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="155">
   <si>
     <t>DB Assignment 0NF</t>
   </si>
@@ -274,12 +277,274 @@
   <si>
     <t>not great</t>
   </si>
+  <si>
+    <t>password</t>
+  </si>
+  <si>
+    <t>www.imageurl.com</t>
+  </si>
+  <si>
+    <t>Kelly
+Dave
+Bob</t>
+  </si>
+  <si>
+    <t>5001
+5002</t>
+  </si>
+  <si>
+    <t>{chatID: 5001, message: "Hello!", senderID: 1}
+{chatID: 5002, message: "Hello Chat 2!", senderID: 1}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Call of Duty 4
+Fall Guys
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Call of Duty
+Fall Guys
+Grand Theft Auto IV
+Europa Universalis IV
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Call of Duty
+Fall Guys
+Grand Theft Auto IV
+Europa Universalis IV
+Pacman
+Goat Simulator
+</t>
+  </si>
+  <si>
+    <t>{game: "Call of Duty 4", text: "not great 2/10", reviewer: "Brian"}</t>
+  </si>
+  <si>
+    <t>Accounts Table</t>
+  </si>
+  <si>
+    <t>username</t>
+  </si>
+  <si>
+    <t>Friends Table</t>
+  </si>
+  <si>
+    <t>friends_since</t>
+  </si>
+  <si>
+    <t>account1_id</t>
+  </si>
+  <si>
+    <t>account2_id</t>
+  </si>
+  <si>
+    <t>Chat Table</t>
+  </si>
+  <si>
+    <t>chat_image</t>
+  </si>
+  <si>
+    <t>OG Gang</t>
+  </si>
+  <si>
+    <t>www.chatimageurl.com</t>
+  </si>
+  <si>
+    <t>Better Group</t>
+  </si>
+  <si>
+    <t>Messages Table</t>
+  </si>
+  <si>
+    <t>sent_by</t>
+  </si>
+  <si>
+    <t>You online?</t>
+  </si>
+  <si>
+    <t>No, go to bed</t>
+  </si>
+  <si>
+    <t>Game bans</t>
+  </si>
+  <si>
+    <t>expires</t>
+  </si>
+  <si>
+    <t>reason</t>
+  </si>
+  <si>
+    <t>abuse of voice chat</t>
+  </si>
+  <si>
+    <t>cheating</t>
+  </si>
+  <si>
+    <t>Game table</t>
+  </si>
+  <si>
+    <t>hardware_requirements</t>
+  </si>
+  <si>
+    <t>publisher</t>
+  </si>
+  <si>
+    <t>release_date</t>
+  </si>
+  <si>
+    <t>Call of Duty 4</t>
+  </si>
+  <si>
+    <t>Fall Guys</t>
+  </si>
+  <si>
+    <t>Grand Theft Auto IV</t>
+  </si>
+  <si>
+    <t>Europa Universalis IV</t>
+  </si>
+  <si>
+    <t>Goat Simulator</t>
+  </si>
+  <si>
+    <t>The original modern warfare experience</t>
+  </si>
+  <si>
+    <t>Family fun obstacle game</t>
+  </si>
+  <si>
+    <t>Dark gritty open world story</t>
+  </si>
+  <si>
+    <t>We yearn for the pretty spreadsheet games</t>
+  </si>
+  <si>
+    <t>Classic</t>
+  </si>
+  <si>
+    <t>I don't know why this exists tbh</t>
+  </si>
+  <si>
+    <t>Infinity Ward</t>
+  </si>
+  <si>
+    <t>Epic Games</t>
+  </si>
+  <si>
+    <t>Rockstar</t>
+  </si>
+  <si>
+    <t>Paradox Interactive</t>
+  </si>
+  <si>
+    <t>Atari</t>
+  </si>
+  <si>
+    <t>Coffee Stain Studios</t>
+  </si>
+  <si>
+    <t>Owned Games</t>
+  </si>
+  <si>
+    <t>date_aquiered</t>
+  </si>
+  <si>
+    <t>Hardware Table</t>
+  </si>
+  <si>
+    <t>mac</t>
+  </si>
+  <si>
+    <t>windows</t>
+  </si>
+  <si>
+    <t>linux</t>
+  </si>
+  <si>
+    <t>min_cpu</t>
+  </si>
+  <si>
+    <t>rec_cpu</t>
+  </si>
+  <si>
+    <t>min_memory</t>
+  </si>
+  <si>
+    <t>rec_memory</t>
+  </si>
+  <si>
+    <t>min_gpu</t>
+  </si>
+  <si>
+    <t>rec_gpu</t>
+  </si>
+  <si>
+    <t>storage</t>
+  </si>
+  <si>
+    <t>intel i9</t>
+  </si>
+  <si>
+    <t>intel i3</t>
+  </si>
+  <si>
+    <t>4gb</t>
+  </si>
+  <si>
+    <t>8gb</t>
+  </si>
+  <si>
+    <t>GTX1050</t>
+  </si>
+  <si>
+    <t>GTX1080</t>
+  </si>
+  <si>
+    <t>20GB</t>
+  </si>
+  <si>
+    <t>amd ryzen 3</t>
+  </si>
+  <si>
+    <t>amd ryzen 5</t>
+  </si>
+  <si>
+    <t>RTX2080</t>
+  </si>
+  <si>
+    <t>40GB</t>
+  </si>
+  <si>
+    <t>Reviews Table</t>
+  </si>
+  <si>
+    <t>written_by</t>
+  </si>
+  <si>
+    <t>Ban Reasons Table</t>
+  </si>
+  <si>
+    <t>ban_id</t>
+  </si>
+  <si>
+    <t>a100</t>
+  </si>
+  <si>
+    <t>a101</t>
+  </si>
+  <si>
+    <t>Voice chat abuse</t>
+  </si>
+  <si>
+    <t>Cheating</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -291,6 +556,14 @@
       <u/>
       <sz val="12"/>
       <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -449,7 +722,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
@@ -471,22 +744,96 @@
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -498,84 +845,101 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -961,13 +1325,13 @@
       <c r="J7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="K7" s="13" t="s">
+      <c r="K7" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="L7" s="13" t="s">
+      <c r="L7" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="M7" s="14" t="s">
+      <c r="M7" s="1" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1019,7 +1383,7 @@
       <c r="L9" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="M9" s="15" t="s">
+      <c r="M9" s="12" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1027,76 +1391,76 @@
       <c r="B13" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
-      <c r="I13" s="10"/>
-      <c r="J13" s="10"/>
-      <c r="K13" s="10"/>
-      <c r="L13" s="10"/>
-      <c r="M13" s="10"/>
-      <c r="N13" s="10"/>
+      <c r="D13" s="35"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="35"/>
+      <c r="G13" s="35"/>
+      <c r="H13" s="35"/>
+      <c r="I13" s="35"/>
+      <c r="J13" s="35"/>
+      <c r="K13" s="35"/>
+      <c r="L13" s="35"/>
+      <c r="M13" s="35"/>
+      <c r="N13" s="35"/>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B14" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11"/>
-      <c r="J14" s="11"/>
-      <c r="K14" s="11"/>
-      <c r="L14" s="11"/>
-      <c r="M14" s="11"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="34"/>
+      <c r="F14" s="34"/>
+      <c r="G14" s="34"/>
+      <c r="H14" s="34"/>
+      <c r="I14" s="34"/>
+      <c r="J14" s="34"/>
+      <c r="K14" s="34"/>
+      <c r="L14" s="34"/>
+      <c r="M14" s="34"/>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="11"/>
-      <c r="J15" s="11"/>
-      <c r="K15" s="11"/>
-      <c r="L15" s="11"/>
-      <c r="M15" s="11"/>
-      <c r="N15" s="11"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="34"/>
+      <c r="G15" s="34"/>
+      <c r="H15" s="34"/>
+      <c r="I15" s="34"/>
+      <c r="J15" s="34"/>
+      <c r="K15" s="34"/>
+      <c r="L15" s="34"/>
+      <c r="M15" s="34"/>
+      <c r="N15" s="34"/>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C16" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="11"/>
-      <c r="J16" s="11"/>
-      <c r="K16" s="11"/>
-      <c r="L16" s="11"/>
-      <c r="M16" s="11"/>
-      <c r="N16" s="11"/>
+      <c r="D16" s="34"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="34"/>
+      <c r="G16" s="34"/>
+      <c r="H16" s="34"/>
+      <c r="I16" s="34"/>
+      <c r="J16" s="34"/>
+      <c r="K16" s="34"/>
+      <c r="L16" s="34"/>
+      <c r="M16" s="34"/>
+      <c r="N16" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1131,372 +1495,372 @@
       </c>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="41" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="19"/>
-      <c r="I6" s="17" t="s">
+      <c r="C6" s="42"/>
+      <c r="D6" s="42"/>
+      <c r="E6" s="42"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="43"/>
+      <c r="I6" s="41" t="s">
         <v>56</v>
       </c>
-      <c r="J6" s="18"/>
-      <c r="K6" s="18"/>
-      <c r="L6" s="19"/>
+      <c r="J6" s="42"/>
+      <c r="K6" s="42"/>
+      <c r="L6" s="43"/>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B7" s="34" t="s">
+      <c r="B7" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="35" t="s">
+      <c r="C7" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="D7" s="35" t="s">
+      <c r="D7" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="E7" s="35" t="s">
+      <c r="E7" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="F7" s="35" t="s">
+      <c r="F7" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="G7" s="36" t="s">
+      <c r="G7" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="I7" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="J7" s="35" t="s">
+      <c r="I7" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="J7" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="K7" s="35" t="s">
+      <c r="K7" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="L7" s="36" t="s">
+      <c r="L7" s="25" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B8" s="37">
-        <v>1</v>
-      </c>
-      <c r="C8" s="38" t="s">
+      <c r="B8" s="26">
+        <v>1</v>
+      </c>
+      <c r="C8" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="38" t="s">
+      <c r="D8" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="E8" s="39" t="s">
+      <c r="E8" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="F8" s="38" t="s">
+      <c r="F8" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="G8" s="40" t="b">
+      <c r="G8" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="I8" s="28">
-        <v>1</v>
-      </c>
-      <c r="J8" s="29">
-        <v>1</v>
-      </c>
-      <c r="K8" s="29" t="s">
+      <c r="I8" s="17">
+        <v>1</v>
+      </c>
+      <c r="J8" s="18">
+        <v>1</v>
+      </c>
+      <c r="K8" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="L8" s="30">
+      <c r="L8" s="19">
         <v>2</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B9" s="16"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
+      <c r="B9" s="13"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="13"/>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="19"/>
-      <c r="E10" s="17" t="s">
+      <c r="C10" s="43"/>
+      <c r="E10" s="41" t="s">
         <v>42</v>
       </c>
-      <c r="F10" s="19"/>
-      <c r="H10" s="17" t="s">
+      <c r="F10" s="43"/>
+      <c r="H10" s="41" t="s">
         <v>45</v>
       </c>
-      <c r="I10" s="19"/>
-      <c r="K10" s="22" t="s">
+      <c r="I10" s="43"/>
+      <c r="K10" s="36" t="s">
         <v>46</v>
       </c>
-      <c r="L10" s="23"/>
-      <c r="M10" s="23"/>
-      <c r="N10" s="24"/>
+      <c r="L10" s="37"/>
+      <c r="M10" s="37"/>
+      <c r="N10" s="38"/>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B11" s="31" t="s">
+      <c r="B11" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="C11" s="33" t="s">
+      <c r="C11" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="E11" s="31" t="s">
+      <c r="E11" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="F11" s="33" t="s">
+      <c r="F11" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="H11" s="31" t="s">
+      <c r="H11" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="I11" s="33" t="s">
-        <v>1</v>
-      </c>
-      <c r="K11" s="31" t="s">
+      <c r="I11" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="K11" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="L11" s="32" t="s">
+      <c r="L11" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="M11" s="32" t="s">
+      <c r="M11" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="N11" s="33" t="s">
+      <c r="N11" s="22" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B12" s="25">
-        <v>1</v>
-      </c>
-      <c r="C12" s="27">
+      <c r="B12" s="14">
+        <v>1</v>
+      </c>
+      <c r="C12" s="16">
         <v>2</v>
       </c>
-      <c r="E12" s="25">
-        <v>1</v>
-      </c>
-      <c r="F12" s="27" t="s">
+      <c r="E12" s="14">
+        <v>1</v>
+      </c>
+      <c r="F12" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="H12" s="25">
-        <v>1</v>
-      </c>
-      <c r="I12" s="27">
-        <v>1</v>
-      </c>
-      <c r="K12" s="25">
+      <c r="H12" s="14">
+        <v>1</v>
+      </c>
+      <c r="I12" s="16">
+        <v>1</v>
+      </c>
+      <c r="K12" s="14">
         <v>178645</v>
       </c>
-      <c r="L12" s="26">
-        <v>1</v>
-      </c>
-      <c r="M12" s="26" t="s">
+      <c r="L12" s="15">
+        <v>1</v>
+      </c>
+      <c r="M12" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="N12" s="27">
+      <c r="N12" s="16">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B13" s="25">
-        <v>1</v>
-      </c>
-      <c r="C13" s="27">
+      <c r="B13" s="14">
+        <v>1</v>
+      </c>
+      <c r="C13" s="16">
         <v>3</v>
       </c>
-      <c r="E13" s="25"/>
-      <c r="F13" s="27"/>
-      <c r="H13" s="28">
-        <v>1</v>
-      </c>
-      <c r="I13" s="30">
+      <c r="E13" s="14"/>
+      <c r="F13" s="16"/>
+      <c r="H13" s="17">
+        <v>1</v>
+      </c>
+      <c r="I13" s="19">
         <v>2</v>
       </c>
-      <c r="K13" s="28">
+      <c r="K13" s="17">
         <v>2664637</v>
       </c>
-      <c r="L13" s="29">
+      <c r="L13" s="18">
         <v>2</v>
       </c>
-      <c r="M13" s="29" t="s">
+      <c r="M13" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="N13" s="30">
+      <c r="N13" s="19">
         <v>1</v>
       </c>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B14" s="28">
-        <v>1</v>
-      </c>
-      <c r="C14" s="30">
+      <c r="B14" s="17">
+        <v>1</v>
+      </c>
+      <c r="C14" s="19">
         <v>4</v>
       </c>
-      <c r="E14" s="28"/>
-      <c r="F14" s="30"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="19"/>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B16" s="22" t="s">
+      <c r="B16" s="36" t="s">
         <v>50</v>
       </c>
-      <c r="C16" s="23"/>
-      <c r="D16" s="23"/>
-      <c r="E16" s="24"/>
-      <c r="G16" s="20" t="s">
+      <c r="C16" s="37"/>
+      <c r="D16" s="37"/>
+      <c r="E16" s="38"/>
+      <c r="G16" s="39" t="s">
         <v>55</v>
       </c>
-      <c r="H16" s="21"/>
-      <c r="J16" s="22" t="s">
+      <c r="H16" s="40"/>
+      <c r="J16" s="36" t="s">
         <v>51</v>
       </c>
-      <c r="K16" s="24"/>
+      <c r="K16" s="38"/>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B17" s="34" t="s">
+      <c r="B17" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="C17" s="35" t="s">
+      <c r="C17" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="D17" s="35" t="s">
+      <c r="D17" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="E17" s="36" t="s">
+      <c r="E17" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="G17" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="H17" s="36" t="s">
+      <c r="G17" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="H17" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="J17" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="K17" s="36" t="s">
+      <c r="J17" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="K17" s="25" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B18" s="41">
-        <v>1</v>
-      </c>
-      <c r="C18" s="42" t="s">
+      <c r="B18" s="30">
+        <v>1</v>
+      </c>
+      <c r="C18" s="31" t="s">
         <v>62</v>
       </c>
-      <c r="D18" s="42" t="s">
+      <c r="D18" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="E18" s="43" t="b">
-        <v>1</v>
-      </c>
-      <c r="G18" s="41">
-        <v>1</v>
-      </c>
-      <c r="H18" s="43">
-        <v>1</v>
-      </c>
-      <c r="J18" s="44">
-        <v>1</v>
-      </c>
-      <c r="K18" s="45">
+      <c r="E18" s="32" t="b">
+        <v>1</v>
+      </c>
+      <c r="G18" s="30">
+        <v>1</v>
+      </c>
+      <c r="H18" s="32">
+        <v>1</v>
+      </c>
+      <c r="J18" s="30">
+        <v>1</v>
+      </c>
+      <c r="K18" s="32">
         <v>1</v>
       </c>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B19" s="41">
+      <c r="B19" s="30">
         <v>2</v>
       </c>
-      <c r="C19" s="42" t="s">
+      <c r="C19" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="D19" s="42" t="s">
+      <c r="D19" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="E19" s="43" t="b">
+      <c r="E19" s="32" t="b">
         <v>0</v>
       </c>
-      <c r="G19" s="41">
-        <v>1</v>
-      </c>
-      <c r="H19" s="43">
+      <c r="G19" s="30">
+        <v>1</v>
+      </c>
+      <c r="H19" s="32">
         <v>2</v>
       </c>
-      <c r="J19" s="44">
-        <v>1</v>
-      </c>
-      <c r="K19" s="45">
+      <c r="J19" s="30">
+        <v>1</v>
+      </c>
+      <c r="K19" s="32">
         <v>2</v>
       </c>
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B20" s="41">
+      <c r="B20" s="30">
         <v>3</v>
       </c>
-      <c r="C20" s="42" t="s">
+      <c r="C20" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="D20" s="42" t="s">
+      <c r="D20" s="31" t="s">
         <v>69</v>
       </c>
-      <c r="E20" s="43" t="b">
+      <c r="E20" s="32" t="b">
         <v>0</v>
       </c>
-      <c r="G20" s="41">
-        <v>1</v>
-      </c>
-      <c r="H20" s="43">
+      <c r="G20" s="30">
+        <v>1</v>
+      </c>
+      <c r="H20" s="32">
         <v>3</v>
       </c>
-      <c r="J20" s="37">
-        <v>1</v>
-      </c>
-      <c r="K20" s="40">
+      <c r="J20" s="26">
+        <v>1</v>
+      </c>
+      <c r="K20" s="29">
         <v>4</v>
       </c>
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B21" s="41">
+      <c r="B21" s="30">
         <v>4</v>
       </c>
-      <c r="C21" s="42" t="s">
+      <c r="C21" s="31" t="s">
         <v>65</v>
       </c>
-      <c r="D21" s="42" t="s">
+      <c r="D21" s="31" t="s">
         <v>70</v>
       </c>
-      <c r="E21" s="43" t="b">
+      <c r="E21" s="32" t="b">
         <v>0</v>
       </c>
-      <c r="G21" s="41">
-        <v>1</v>
-      </c>
-      <c r="H21" s="43">
+      <c r="G21" s="30">
+        <v>1</v>
+      </c>
+      <c r="H21" s="32">
         <v>4</v>
       </c>
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B22" s="37">
+      <c r="B22" s="26">
         <v>5</v>
       </c>
-      <c r="C22" s="38" t="s">
+      <c r="C22" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="D22" s="38" t="s">
+      <c r="D22" s="27" t="s">
         <v>71</v>
       </c>
-      <c r="E22" s="40" t="b">
-        <v>1</v>
-      </c>
-      <c r="G22" s="37">
-        <v>1</v>
-      </c>
-      <c r="H22" s="40">
+      <c r="E22" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="G22" s="26">
+        <v>1</v>
+      </c>
+      <c r="H22" s="29">
         <v>5</v>
       </c>
     </row>
@@ -1517,4 +1881,1362 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28D27225-4E2F-3547-94B1-A60903264212}">
+  <dimension ref="B2:N8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="2.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="44.1640625" customWidth="1"/>
+    <col min="10" max="10" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19" customWidth="1"/>
+    <col min="13" max="13" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="51" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B2" s="56" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" s="57" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2" s="57" t="s">
+        <v>73</v>
+      </c>
+      <c r="E2" s="57" t="s">
+        <v>38</v>
+      </c>
+      <c r="F2" s="57" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="57" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="57" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="57" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="L2" s="57" t="s">
+        <v>11</v>
+      </c>
+      <c r="M2" s="57" t="s">
+        <v>12</v>
+      </c>
+      <c r="N2" s="58" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B3" s="45"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="46"/>
+      <c r="H3" s="46"/>
+      <c r="I3" s="46"/>
+      <c r="J3" s="46"/>
+      <c r="K3" s="46"/>
+      <c r="L3" s="46"/>
+      <c r="M3" s="46"/>
+      <c r="N3" s="47"/>
+    </row>
+    <row r="4" spans="2:14" ht="119" x14ac:dyDescent="0.2">
+      <c r="B4" s="48">
+        <v>1</v>
+      </c>
+      <c r="C4" s="49" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="49" t="s">
+        <v>73</v>
+      </c>
+      <c r="E4" s="50" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="50" t="s">
+        <v>74</v>
+      </c>
+      <c r="G4" s="51" t="s">
+        <v>75</v>
+      </c>
+      <c r="H4" s="51" t="s">
+        <v>76</v>
+      </c>
+      <c r="I4" s="51" t="s">
+        <v>77</v>
+      </c>
+      <c r="J4" s="49" t="b">
+        <v>0</v>
+      </c>
+      <c r="K4" s="51" t="s">
+        <v>78</v>
+      </c>
+      <c r="L4" s="51" t="s">
+        <v>80</v>
+      </c>
+      <c r="M4" s="51" t="s">
+        <v>79</v>
+      </c>
+      <c r="N4" s="52" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B8" s="44"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E4" r:id="rId1" xr:uid="{7ABA0B8C-E3DF-2848-8BD0-C145B98B063F}"/>
+    <hyperlink ref="F4" r:id="rId2" xr:uid="{B6ACBE81-D5C2-D247-A3F7-37EAC222B135}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A068AD79-5318-BC43-B234-A0F4C6006838}">
+  <dimension ref="B3:V31"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.83203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.5" customWidth="1"/>
+    <col min="14" max="14" width="10.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B3" t="s">
+        <v>82</v>
+      </c>
+      <c r="J3" s="61" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="5" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B5" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="54" t="s">
+        <v>83</v>
+      </c>
+      <c r="D5" s="54" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" s="54" t="s">
+        <v>73</v>
+      </c>
+      <c r="F5" s="54" t="s">
+        <v>5</v>
+      </c>
+      <c r="G5" s="55" t="s">
+        <v>9</v>
+      </c>
+      <c r="J5" s="64" t="s">
+        <v>148</v>
+      </c>
+      <c r="K5" s="65" t="s">
+        <v>52</v>
+      </c>
+      <c r="L5" s="65" t="s">
+        <v>49</v>
+      </c>
+      <c r="M5" s="66" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="6" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B6" s="48">
+        <v>1</v>
+      </c>
+      <c r="C6" s="49" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="50" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="49" t="s">
+        <v>73</v>
+      </c>
+      <c r="F6" s="50" t="s">
+        <v>74</v>
+      </c>
+      <c r="G6" s="52" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" s="48">
+        <v>1</v>
+      </c>
+      <c r="K6" s="49">
+        <v>5000</v>
+      </c>
+      <c r="L6" s="49" t="s">
+        <v>72</v>
+      </c>
+      <c r="M6" s="52">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B9" t="s">
+        <v>84</v>
+      </c>
+      <c r="F9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="11" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B11" s="53" t="s">
+        <v>86</v>
+      </c>
+      <c r="C11" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="D11" s="55" t="s">
+        <v>85</v>
+      </c>
+      <c r="F11" s="64" t="s">
+        <v>43</v>
+      </c>
+      <c r="G11" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="H11" s="66" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="12" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B12" s="45">
+        <v>1</v>
+      </c>
+      <c r="C12" s="46">
+        <v>2</v>
+      </c>
+      <c r="D12" s="59">
+        <v>45717</v>
+      </c>
+      <c r="F12" s="45">
+        <v>200</v>
+      </c>
+      <c r="G12" s="46" t="s">
+        <v>90</v>
+      </c>
+      <c r="H12" s="62" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="13" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B13" s="48">
+        <v>3</v>
+      </c>
+      <c r="C13" s="49">
+        <v>4</v>
+      </c>
+      <c r="D13" s="60">
+        <v>45716</v>
+      </c>
+      <c r="F13" s="48">
+        <v>201</v>
+      </c>
+      <c r="G13" s="49" t="s">
+        <v>92</v>
+      </c>
+      <c r="H13" s="63" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="16" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B16" t="s">
+        <v>93</v>
+      </c>
+      <c r="G16" s="61" t="s">
+        <v>97</v>
+      </c>
+      <c r="L16" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="18" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B18" s="53" t="s">
+        <v>47</v>
+      </c>
+      <c r="C18" s="54" t="s">
+        <v>42</v>
+      </c>
+      <c r="D18" s="54" t="s">
+        <v>94</v>
+      </c>
+      <c r="E18" s="55" t="s">
+        <v>46</v>
+      </c>
+      <c r="G18" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="H18" s="65" t="s">
+        <v>52</v>
+      </c>
+      <c r="I18" s="65" t="s">
+        <v>98</v>
+      </c>
+      <c r="J18" s="66" t="s">
+        <v>99</v>
+      </c>
+      <c r="L18" s="64" t="s">
+        <v>34</v>
+      </c>
+      <c r="M18" s="65" t="s">
+        <v>126</v>
+      </c>
+      <c r="N18" s="65" t="s">
+        <v>127</v>
+      </c>
+      <c r="O18" s="65" t="s">
+        <v>128</v>
+      </c>
+      <c r="P18" s="65" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q18" s="65" t="s">
+        <v>130</v>
+      </c>
+      <c r="R18" s="65" t="s">
+        <v>131</v>
+      </c>
+      <c r="S18" s="65" t="s">
+        <v>132</v>
+      </c>
+      <c r="T18" s="65" t="s">
+        <v>133</v>
+      </c>
+      <c r="U18" s="65" t="s">
+        <v>134</v>
+      </c>
+      <c r="V18" s="66" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="19" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B19" s="45">
+        <v>2000</v>
+      </c>
+      <c r="C19" s="46">
+        <v>200</v>
+      </c>
+      <c r="D19" s="46">
+        <v>1</v>
+      </c>
+      <c r="E19" s="47" t="s">
+        <v>95</v>
+      </c>
+      <c r="G19" s="67">
+        <v>1</v>
+      </c>
+      <c r="H19" s="61">
+        <v>5000</v>
+      </c>
+      <c r="I19" s="68">
+        <v>45748</v>
+      </c>
+      <c r="J19" s="47" t="s">
+        <v>100</v>
+      </c>
+      <c r="L19" s="67">
+        <v>12000</v>
+      </c>
+      <c r="M19" s="46" t="b">
+        <v>0</v>
+      </c>
+      <c r="N19" s="46" t="b">
+        <v>1</v>
+      </c>
+      <c r="O19" s="46" t="b">
+        <v>0</v>
+      </c>
+      <c r="P19" s="46" t="s">
+        <v>137</v>
+      </c>
+      <c r="Q19" s="46" t="s">
+        <v>136</v>
+      </c>
+      <c r="R19" s="46" t="s">
+        <v>138</v>
+      </c>
+      <c r="S19" s="46" t="s">
+        <v>139</v>
+      </c>
+      <c r="T19" s="46" t="s">
+        <v>140</v>
+      </c>
+      <c r="U19" s="46" t="s">
+        <v>141</v>
+      </c>
+      <c r="V19" s="47" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="20" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B20" s="48">
+        <v>2003</v>
+      </c>
+      <c r="C20" s="49">
+        <v>200</v>
+      </c>
+      <c r="D20" s="49">
+        <v>2</v>
+      </c>
+      <c r="E20" s="52" t="s">
+        <v>96</v>
+      </c>
+      <c r="G20" s="69">
+        <v>1</v>
+      </c>
+      <c r="H20" s="49">
+        <v>5001</v>
+      </c>
+      <c r="I20" s="70">
+        <v>2958352</v>
+      </c>
+      <c r="J20" s="52" t="s">
+        <v>101</v>
+      </c>
+      <c r="L20" s="69">
+        <v>12111</v>
+      </c>
+      <c r="M20" s="49" t="b">
+        <v>1</v>
+      </c>
+      <c r="N20" s="49" t="b">
+        <v>1</v>
+      </c>
+      <c r="O20" s="49" t="b">
+        <v>1</v>
+      </c>
+      <c r="P20" s="49" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q20" s="49" t="s">
+        <v>144</v>
+      </c>
+      <c r="R20" s="49" t="s">
+        <v>138</v>
+      </c>
+      <c r="S20" s="49" t="s">
+        <v>139</v>
+      </c>
+      <c r="T20" s="49" t="s">
+        <v>141</v>
+      </c>
+      <c r="U20" s="49" t="s">
+        <v>145</v>
+      </c>
+      <c r="V20" s="52" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="23" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B23" t="s">
+        <v>102</v>
+      </c>
+      <c r="J23" s="61" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="24" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B24" s="10"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="10"/>
+      <c r="H24" s="10"/>
+    </row>
+    <row r="25" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B25" s="53" t="s">
+        <v>52</v>
+      </c>
+      <c r="C25" s="54" t="s">
+        <v>36</v>
+      </c>
+      <c r="D25" s="54" t="s">
+        <v>53</v>
+      </c>
+      <c r="E25" s="54" t="s">
+        <v>54</v>
+      </c>
+      <c r="F25" s="54" t="s">
+        <v>103</v>
+      </c>
+      <c r="G25" s="54" t="s">
+        <v>104</v>
+      </c>
+      <c r="H25" s="55" t="s">
+        <v>105</v>
+      </c>
+      <c r="J25" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="K25" s="65" t="s">
+        <v>52</v>
+      </c>
+      <c r="L25" s="66" t="s">
+        <v>124</v>
+      </c>
+      <c r="N25" s="61"/>
+    </row>
+    <row r="26" spans="2:22" ht="68" x14ac:dyDescent="0.2">
+      <c r="B26" s="45">
+        <v>5000</v>
+      </c>
+      <c r="C26" s="46" t="s">
+        <v>106</v>
+      </c>
+      <c r="D26" s="71" t="s">
+        <v>111</v>
+      </c>
+      <c r="E26" s="46" t="b">
+        <v>1</v>
+      </c>
+      <c r="F26" s="46">
+        <v>12000</v>
+      </c>
+      <c r="G26" s="46" t="s">
+        <v>117</v>
+      </c>
+      <c r="H26" s="59">
+        <v>39391</v>
+      </c>
+      <c r="J26" s="72">
+        <v>1</v>
+      </c>
+      <c r="K26" s="46">
+        <v>5000</v>
+      </c>
+      <c r="L26" s="59">
+        <v>45658</v>
+      </c>
+    </row>
+    <row r="27" spans="2:22" ht="34" x14ac:dyDescent="0.2">
+      <c r="B27" s="45">
+        <v>5001</v>
+      </c>
+      <c r="C27" s="46" t="s">
+        <v>107</v>
+      </c>
+      <c r="D27" s="71" t="s">
+        <v>112</v>
+      </c>
+      <c r="E27" s="46" t="b">
+        <v>1</v>
+      </c>
+      <c r="F27" s="46">
+        <v>12111</v>
+      </c>
+      <c r="G27" s="46" t="s">
+        <v>118</v>
+      </c>
+      <c r="H27" s="59">
+        <v>44047</v>
+      </c>
+      <c r="J27" s="72">
+        <v>1</v>
+      </c>
+      <c r="K27" s="46">
+        <v>5001</v>
+      </c>
+      <c r="L27" s="59">
+        <v>45658</v>
+      </c>
+    </row>
+    <row r="28" spans="2:22" ht="51" x14ac:dyDescent="0.2">
+      <c r="B28" s="45">
+        <v>5002</v>
+      </c>
+      <c r="C28" s="46" t="s">
+        <v>108</v>
+      </c>
+      <c r="D28" s="71" t="s">
+        <v>113</v>
+      </c>
+      <c r="E28" s="46" t="b">
+        <v>1</v>
+      </c>
+      <c r="F28" s="46">
+        <v>12222</v>
+      </c>
+      <c r="G28" s="46" t="s">
+        <v>119</v>
+      </c>
+      <c r="H28" s="59">
+        <v>39567</v>
+      </c>
+      <c r="J28" s="72">
+        <v>1</v>
+      </c>
+      <c r="K28" s="46">
+        <v>5002</v>
+      </c>
+      <c r="L28" s="59">
+        <v>45658</v>
+      </c>
+    </row>
+    <row r="29" spans="2:22" ht="68" x14ac:dyDescent="0.2">
+      <c r="B29" s="45">
+        <v>5003</v>
+      </c>
+      <c r="C29" s="46" t="s">
+        <v>109</v>
+      </c>
+      <c r="D29" s="71" t="s">
+        <v>114</v>
+      </c>
+      <c r="E29" s="46" t="b">
+        <v>1</v>
+      </c>
+      <c r="F29" s="46">
+        <v>12333</v>
+      </c>
+      <c r="G29" s="46" t="s">
+        <v>120</v>
+      </c>
+      <c r="H29" s="59">
+        <v>41499</v>
+      </c>
+      <c r="J29" s="72">
+        <v>1</v>
+      </c>
+      <c r="K29" s="46">
+        <v>5003</v>
+      </c>
+      <c r="L29" s="59">
+        <v>45658</v>
+      </c>
+    </row>
+    <row r="30" spans="2:22" ht="17" x14ac:dyDescent="0.2">
+      <c r="B30" s="45">
+        <v>5004</v>
+      </c>
+      <c r="C30" s="46" t="s">
+        <v>65</v>
+      </c>
+      <c r="D30" s="71" t="s">
+        <v>115</v>
+      </c>
+      <c r="E30" s="46" t="b">
+        <v>0</v>
+      </c>
+      <c r="F30" s="46">
+        <v>12444</v>
+      </c>
+      <c r="G30" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="H30" s="59">
+        <v>29363</v>
+      </c>
+      <c r="J30" s="72">
+        <v>1</v>
+      </c>
+      <c r="K30" s="46">
+        <v>5004</v>
+      </c>
+      <c r="L30" s="59">
+        <v>45658</v>
+      </c>
+    </row>
+    <row r="31" spans="2:22" ht="51" x14ac:dyDescent="0.2">
+      <c r="B31" s="48">
+        <v>5005</v>
+      </c>
+      <c r="C31" s="49" t="s">
+        <v>110</v>
+      </c>
+      <c r="D31" s="51" t="s">
+        <v>116</v>
+      </c>
+      <c r="E31" s="49" t="b">
+        <v>0</v>
+      </c>
+      <c r="F31" s="49">
+        <v>12555</v>
+      </c>
+      <c r="G31" s="49" t="s">
+        <v>122</v>
+      </c>
+      <c r="H31" s="60">
+        <v>41730</v>
+      </c>
+      <c r="J31" s="73">
+        <v>1</v>
+      </c>
+      <c r="K31" s="49">
+        <v>5005</v>
+      </c>
+      <c r="L31" s="60">
+        <v>45658</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D6" r:id="rId1" xr:uid="{4EB8137E-9A4F-6542-88DC-A2E06382059F}"/>
+    <hyperlink ref="F6" r:id="rId2" xr:uid="{AA3954D5-B29F-3942-A108-66548BFF6A72}"/>
+    <hyperlink ref="H12" r:id="rId3" xr:uid="{9BF7125A-17C1-E44B-9BC1-491303B68FEB}"/>
+    <hyperlink ref="H13" r:id="rId4" xr:uid="{DCDE004D-8F7A-E94C-9479-AC06B0DF7ABF}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFC77903-378C-CC46-A030-21BE4854BEF3}">
+  <dimension ref="B3:V31"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.83203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="7.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B3" t="s">
+        <v>82</v>
+      </c>
+      <c r="J3" s="61" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="5" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B5" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="54" t="s">
+        <v>83</v>
+      </c>
+      <c r="D5" s="54" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" s="54" t="s">
+        <v>73</v>
+      </c>
+      <c r="F5" s="54" t="s">
+        <v>5</v>
+      </c>
+      <c r="G5" s="55" t="s">
+        <v>9</v>
+      </c>
+      <c r="J5" s="64" t="s">
+        <v>148</v>
+      </c>
+      <c r="K5" s="65" t="s">
+        <v>52</v>
+      </c>
+      <c r="L5" s="65" t="s">
+        <v>49</v>
+      </c>
+      <c r="M5" s="66" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="6" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B6" s="48">
+        <v>1</v>
+      </c>
+      <c r="C6" s="49" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="50" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="49" t="s">
+        <v>73</v>
+      </c>
+      <c r="F6" s="50" t="s">
+        <v>74</v>
+      </c>
+      <c r="G6" s="52" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" s="48">
+        <v>1</v>
+      </c>
+      <c r="K6" s="49">
+        <v>5000</v>
+      </c>
+      <c r="L6" s="49" t="s">
+        <v>72</v>
+      </c>
+      <c r="M6" s="52">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B9" t="s">
+        <v>84</v>
+      </c>
+      <c r="F9" t="s">
+        <v>88</v>
+      </c>
+      <c r="J9" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="11" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B11" s="53" t="s">
+        <v>86</v>
+      </c>
+      <c r="C11" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="D11" s="55" t="s">
+        <v>85</v>
+      </c>
+      <c r="F11" s="64" t="s">
+        <v>43</v>
+      </c>
+      <c r="G11" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="H11" s="66" t="s">
+        <v>89</v>
+      </c>
+      <c r="J11" s="64" t="s">
+        <v>150</v>
+      </c>
+      <c r="K11" s="66" t="s">
+        <v>99</v>
+      </c>
+      <c r="L11" s="61"/>
+    </row>
+    <row r="12" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B12" s="45">
+        <v>1</v>
+      </c>
+      <c r="C12" s="46">
+        <v>2</v>
+      </c>
+      <c r="D12" s="59">
+        <v>45717</v>
+      </c>
+      <c r="F12" s="45">
+        <v>200</v>
+      </c>
+      <c r="G12" s="46" t="s">
+        <v>90</v>
+      </c>
+      <c r="H12" s="62" t="s">
+        <v>91</v>
+      </c>
+      <c r="J12" s="75" t="s">
+        <v>151</v>
+      </c>
+      <c r="K12" s="76" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="13" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B13" s="48">
+        <v>3</v>
+      </c>
+      <c r="C13" s="49">
+        <v>4</v>
+      </c>
+      <c r="D13" s="60">
+        <v>45716</v>
+      </c>
+      <c r="F13" s="48">
+        <v>201</v>
+      </c>
+      <c r="G13" s="49" t="s">
+        <v>92</v>
+      </c>
+      <c r="H13" s="63" t="s">
+        <v>91</v>
+      </c>
+      <c r="J13" s="77" t="s">
+        <v>152</v>
+      </c>
+      <c r="K13" s="78" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="16" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B16" t="s">
+        <v>93</v>
+      </c>
+      <c r="G16" s="61" t="s">
+        <v>97</v>
+      </c>
+      <c r="L16" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="18" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B18" s="53" t="s">
+        <v>47</v>
+      </c>
+      <c r="C18" s="54" t="s">
+        <v>42</v>
+      </c>
+      <c r="D18" s="54" t="s">
+        <v>94</v>
+      </c>
+      <c r="E18" s="55" t="s">
+        <v>46</v>
+      </c>
+      <c r="G18" s="64" t="s">
+        <v>150</v>
+      </c>
+      <c r="H18" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="I18" s="65" t="s">
+        <v>52</v>
+      </c>
+      <c r="J18" s="66" t="s">
+        <v>98</v>
+      </c>
+      <c r="L18" s="64" t="s">
+        <v>34</v>
+      </c>
+      <c r="M18" s="65" t="s">
+        <v>126</v>
+      </c>
+      <c r="N18" s="65" t="s">
+        <v>127</v>
+      </c>
+      <c r="O18" s="65" t="s">
+        <v>128</v>
+      </c>
+      <c r="P18" s="65" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q18" s="65" t="s">
+        <v>130</v>
+      </c>
+      <c r="R18" s="65" t="s">
+        <v>131</v>
+      </c>
+      <c r="S18" s="65" t="s">
+        <v>132</v>
+      </c>
+      <c r="T18" s="65" t="s">
+        <v>133</v>
+      </c>
+      <c r="U18" s="65" t="s">
+        <v>134</v>
+      </c>
+      <c r="V18" s="66" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="19" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B19" s="45">
+        <v>2000</v>
+      </c>
+      <c r="C19" s="46">
+        <v>200</v>
+      </c>
+      <c r="D19" s="46">
+        <v>1</v>
+      </c>
+      <c r="E19" s="47" t="s">
+        <v>95</v>
+      </c>
+      <c r="G19" s="75" t="s">
+        <v>151</v>
+      </c>
+      <c r="H19" s="61">
+        <v>1</v>
+      </c>
+      <c r="I19" s="61">
+        <v>5000</v>
+      </c>
+      <c r="J19" s="59">
+        <v>45748</v>
+      </c>
+      <c r="L19" s="67">
+        <v>12000</v>
+      </c>
+      <c r="M19" s="46" t="b">
+        <v>0</v>
+      </c>
+      <c r="N19" s="46" t="b">
+        <v>1</v>
+      </c>
+      <c r="O19" s="46" t="b">
+        <v>0</v>
+      </c>
+      <c r="P19" s="46" t="s">
+        <v>137</v>
+      </c>
+      <c r="Q19" s="46" t="s">
+        <v>136</v>
+      </c>
+      <c r="R19" s="46" t="s">
+        <v>138</v>
+      </c>
+      <c r="S19" s="46" t="s">
+        <v>139</v>
+      </c>
+      <c r="T19" s="46" t="s">
+        <v>140</v>
+      </c>
+      <c r="U19" s="46" t="s">
+        <v>141</v>
+      </c>
+      <c r="V19" s="47" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="20" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B20" s="48">
+        <v>2003</v>
+      </c>
+      <c r="C20" s="49">
+        <v>200</v>
+      </c>
+      <c r="D20" s="49">
+        <v>2</v>
+      </c>
+      <c r="E20" s="52" t="s">
+        <v>96</v>
+      </c>
+      <c r="G20" s="69" t="s">
+        <v>152</v>
+      </c>
+      <c r="H20" s="74">
+        <v>1</v>
+      </c>
+      <c r="I20" s="49">
+        <v>5001</v>
+      </c>
+      <c r="J20" s="60">
+        <v>2958352</v>
+      </c>
+      <c r="L20" s="69">
+        <v>12111</v>
+      </c>
+      <c r="M20" s="49" t="b">
+        <v>1</v>
+      </c>
+      <c r="N20" s="49" t="b">
+        <v>1</v>
+      </c>
+      <c r="O20" s="49" t="b">
+        <v>1</v>
+      </c>
+      <c r="P20" s="49" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q20" s="49" t="s">
+        <v>144</v>
+      </c>
+      <c r="R20" s="49" t="s">
+        <v>138</v>
+      </c>
+      <c r="S20" s="49" t="s">
+        <v>139</v>
+      </c>
+      <c r="T20" s="49" t="s">
+        <v>141</v>
+      </c>
+      <c r="U20" s="49" t="s">
+        <v>145</v>
+      </c>
+      <c r="V20" s="52" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="23" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B23" t="s">
+        <v>102</v>
+      </c>
+      <c r="J23" s="61" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="24" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B24" s="10"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="10"/>
+      <c r="H24" s="10"/>
+    </row>
+    <row r="25" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B25" s="53" t="s">
+        <v>52</v>
+      </c>
+      <c r="C25" s="54" t="s">
+        <v>36</v>
+      </c>
+      <c r="D25" s="54" t="s">
+        <v>53</v>
+      </c>
+      <c r="E25" s="54" t="s">
+        <v>54</v>
+      </c>
+      <c r="F25" s="54" t="s">
+        <v>103</v>
+      </c>
+      <c r="G25" s="54" t="s">
+        <v>104</v>
+      </c>
+      <c r="H25" s="55" t="s">
+        <v>105</v>
+      </c>
+      <c r="J25" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="K25" s="65" t="s">
+        <v>52</v>
+      </c>
+      <c r="L25" s="66" t="s">
+        <v>124</v>
+      </c>
+      <c r="N25" s="61"/>
+    </row>
+    <row r="26" spans="2:22" ht="68" x14ac:dyDescent="0.2">
+      <c r="B26" s="45">
+        <v>5000</v>
+      </c>
+      <c r="C26" s="46" t="s">
+        <v>106</v>
+      </c>
+      <c r="D26" s="71" t="s">
+        <v>111</v>
+      </c>
+      <c r="E26" s="46" t="b">
+        <v>1</v>
+      </c>
+      <c r="F26" s="46">
+        <v>12000</v>
+      </c>
+      <c r="G26" s="46" t="s">
+        <v>117</v>
+      </c>
+      <c r="H26" s="59">
+        <v>39391</v>
+      </c>
+      <c r="J26" s="72">
+        <v>1</v>
+      </c>
+      <c r="K26" s="46">
+        <v>5000</v>
+      </c>
+      <c r="L26" s="59">
+        <v>45658</v>
+      </c>
+    </row>
+    <row r="27" spans="2:22" ht="34" x14ac:dyDescent="0.2">
+      <c r="B27" s="45">
+        <v>5001</v>
+      </c>
+      <c r="C27" s="46" t="s">
+        <v>107</v>
+      </c>
+      <c r="D27" s="71" t="s">
+        <v>112</v>
+      </c>
+      <c r="E27" s="46" t="b">
+        <v>1</v>
+      </c>
+      <c r="F27" s="46">
+        <v>12111</v>
+      </c>
+      <c r="G27" s="46" t="s">
+        <v>118</v>
+      </c>
+      <c r="H27" s="59">
+        <v>44047</v>
+      </c>
+      <c r="J27" s="72">
+        <v>1</v>
+      </c>
+      <c r="K27" s="46">
+        <v>5001</v>
+      </c>
+      <c r="L27" s="59">
+        <v>45658</v>
+      </c>
+    </row>
+    <row r="28" spans="2:22" ht="51" x14ac:dyDescent="0.2">
+      <c r="B28" s="45">
+        <v>5002</v>
+      </c>
+      <c r="C28" s="46" t="s">
+        <v>108</v>
+      </c>
+      <c r="D28" s="71" t="s">
+        <v>113</v>
+      </c>
+      <c r="E28" s="46" t="b">
+        <v>1</v>
+      </c>
+      <c r="F28" s="46">
+        <v>12222</v>
+      </c>
+      <c r="G28" s="46" t="s">
+        <v>119</v>
+      </c>
+      <c r="H28" s="59">
+        <v>39567</v>
+      </c>
+      <c r="J28" s="72">
+        <v>1</v>
+      </c>
+      <c r="K28" s="46">
+        <v>5002</v>
+      </c>
+      <c r="L28" s="59">
+        <v>45658</v>
+      </c>
+    </row>
+    <row r="29" spans="2:22" ht="68" x14ac:dyDescent="0.2">
+      <c r="B29" s="45">
+        <v>5003</v>
+      </c>
+      <c r="C29" s="46" t="s">
+        <v>109</v>
+      </c>
+      <c r="D29" s="71" t="s">
+        <v>114</v>
+      </c>
+      <c r="E29" s="46" t="b">
+        <v>1</v>
+      </c>
+      <c r="F29" s="46">
+        <v>12333</v>
+      </c>
+      <c r="G29" s="46" t="s">
+        <v>120</v>
+      </c>
+      <c r="H29" s="59">
+        <v>41499</v>
+      </c>
+      <c r="J29" s="72">
+        <v>1</v>
+      </c>
+      <c r="K29" s="46">
+        <v>5003</v>
+      </c>
+      <c r="L29" s="59">
+        <v>45658</v>
+      </c>
+    </row>
+    <row r="30" spans="2:22" ht="17" x14ac:dyDescent="0.2">
+      <c r="B30" s="45">
+        <v>5004</v>
+      </c>
+      <c r="C30" s="46" t="s">
+        <v>65</v>
+      </c>
+      <c r="D30" s="71" t="s">
+        <v>115</v>
+      </c>
+      <c r="E30" s="46" t="b">
+        <v>0</v>
+      </c>
+      <c r="F30" s="46">
+        <v>12444</v>
+      </c>
+      <c r="G30" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="H30" s="59">
+        <v>29363</v>
+      </c>
+      <c r="J30" s="72">
+        <v>1</v>
+      </c>
+      <c r="K30" s="46">
+        <v>5004</v>
+      </c>
+      <c r="L30" s="59">
+        <v>45658</v>
+      </c>
+    </row>
+    <row r="31" spans="2:22" ht="51" x14ac:dyDescent="0.2">
+      <c r="B31" s="48">
+        <v>5005</v>
+      </c>
+      <c r="C31" s="49" t="s">
+        <v>110</v>
+      </c>
+      <c r="D31" s="51" t="s">
+        <v>116</v>
+      </c>
+      <c r="E31" s="49" t="b">
+        <v>0</v>
+      </c>
+      <c r="F31" s="49">
+        <v>12555</v>
+      </c>
+      <c r="G31" s="49" t="s">
+        <v>122</v>
+      </c>
+      <c r="H31" s="60">
+        <v>41730</v>
+      </c>
+      <c r="J31" s="73">
+        <v>1</v>
+      </c>
+      <c r="K31" s="49">
+        <v>5005</v>
+      </c>
+      <c r="L31" s="60">
+        <v>45658</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D6" r:id="rId1" xr:uid="{3F1792EC-7E94-FF4E-B6EC-C29ABBE8A6A9}"/>
+    <hyperlink ref="F6" r:id="rId2" xr:uid="{82231DA0-9D97-0D4D-9F5E-113A9621E74A}"/>
+    <hyperlink ref="H12" r:id="rId3" xr:uid="{EA434A4B-10C2-0D4E-8287-EE45B8BD325D}"/>
+    <hyperlink ref="H13" r:id="rId4" xr:uid="{FD12E3DD-CAE0-5D46-8931-F669A4B68FE6}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/assignment/normalization_examples/Normalisation.xlsx
+++ b/assignment/normalization_examples/Normalisation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/connorrobinson/Documents/Repos/Relational-Databases/assignment/normalization_examples/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DD11A4E-E2F3-8647-B19A-4A234C68F882}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FBB2694-B8FA-BC47-AC8A-25B30AE6870F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20040" activeTab="4" xr2:uid="{4F075678-4195-7143-B183-D28923453708}"/>
+    <workbookView xWindow="51200" yWindow="5900" windowWidth="34560" windowHeight="21600" activeTab="6" xr2:uid="{4F075678-4195-7143-B183-D28923453708}"/>
   </bookViews>
   <sheets>
     <sheet name="0NF" sheetId="1" r:id="rId1"/>
@@ -18,8 +18,10 @@
     <sheet name="0NF 2.0" sheetId="3" r:id="rId3"/>
     <sheet name="1NF 2.0" sheetId="4" r:id="rId4"/>
     <sheet name="BCNF" sheetId="5" r:id="rId5"/>
+    <sheet name="Queries" sheetId="6" r:id="rId6"/>
+    <sheet name="UNF 3.0" sheetId="7" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="222">
   <si>
     <t>DB Assignment 0NF</t>
   </si>
@@ -538,6 +540,234 @@
   </si>
   <si>
     <t>Cheating</t>
+  </si>
+  <si>
+    <t>User in chat</t>
+  </si>
+  <si>
+    <t>role</t>
+  </si>
+  <si>
+    <t>owner</t>
+  </si>
+  <si>
+    <t>member</t>
+  </si>
+  <si>
+    <t>date_aquired</t>
+  </si>
+  <si>
+    <t>System Requirements</t>
+  </si>
+  <si>
+    <t>system_req_id</t>
+  </si>
+  <si>
+    <t>cpu</t>
+  </si>
+  <si>
+    <t>memory</t>
+  </si>
+  <si>
+    <t>gpu</t>
+  </si>
+  <si>
+    <t>X100</t>
+  </si>
+  <si>
+    <t>X101</t>
+  </si>
+  <si>
+    <t>X102</t>
+  </si>
+  <si>
+    <t>X103</t>
+  </si>
+  <si>
+    <t>4GB</t>
+  </si>
+  <si>
+    <t>8GB</t>
+  </si>
+  <si>
+    <t>AMD Ryzen 3</t>
+  </si>
+  <si>
+    <t>AMD Ryzen 5</t>
+  </si>
+  <si>
+    <t>GTX 1080</t>
+  </si>
+  <si>
+    <t>platform</t>
+  </si>
+  <si>
+    <t>hardware_id</t>
+  </si>
+  <si>
+    <t>min_requirement</t>
+  </si>
+  <si>
+    <t>rec_requirement</t>
+  </si>
+  <si>
+    <t>vr</t>
+  </si>
+  <si>
+    <t>Query</t>
+  </si>
+  <si>
+    <t>Tables Required</t>
+  </si>
+  <si>
+    <t>show available games in store</t>
+  </si>
+  <si>
+    <t>Games</t>
+  </si>
+  <si>
+    <t>Account
+Games
+Owned Games (to know which ones to filter out)</t>
+  </si>
+  <si>
+    <t>show games library</t>
+  </si>
+  <si>
+    <t>buy game</t>
+  </si>
+  <si>
+    <t>add friend</t>
+  </si>
+  <si>
+    <t>Friends
+Account</t>
+  </si>
+  <si>
+    <t>show friends</t>
+  </si>
+  <si>
+    <t>view chat</t>
+  </si>
+  <si>
+    <t>Potential User Queries (Conceptual)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chat
+Message
+Account
+Freinds
+</t>
+  </si>
+  <si>
+    <t>send message</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chat
+Message
+Friends
+Account
+</t>
+  </si>
+  <si>
+    <t>view bans</t>
+  </si>
+  <si>
+    <t>Account
+Owned Games
+Bans</t>
+  </si>
+  <si>
+    <t>Potential Platform Queries</t>
+  </si>
+  <si>
+    <t>add game to store</t>
+  </si>
+  <si>
+    <t>change game price</t>
+  </si>
+  <si>
+    <t>ban user</t>
+  </si>
+  <si>
+    <t>Account</t>
+  </si>
+  <si>
+    <t>ban user for a game</t>
+  </si>
+  <si>
+    <t>Account
+Game Bans</t>
+  </si>
+  <si>
+    <t>Un-normalized Data</t>
+  </si>
+  <si>
+    <t>email-address</t>
+  </si>
+  <si>
+    <t>nairb</t>
+  </si>
+  <si>
+    <t>www.picurl.com</t>
+  </si>
+  <si>
+    <t>has_games</t>
+  </si>
+  <si>
+    <t>{cod 4, true, shooter, windows only, infinity ward, 2009}
+{eu4, true, 4x strategy, multi-platform, paradox interactive, 2014}</t>
+  </si>
+  <si>
+    <t>Fortnite: Abusive Comms
+Monopoly: Cheating
+Halo: Reach: ban revoked</t>
+  </si>
+  <si>
+    <t>ben@db.com
+jame@db.com
+bob@db.com
+gavin@db.com</t>
+  </si>
+  <si>
+    <t>1
+3
+5
+6</t>
+  </si>
+  <si>
+    <t>messages</t>
+  </si>
+  <si>
+    <t>{chat: 1, message: "hi!, timestamp: 2025-01-01},
+{chat: 3, message: "wassup", timestamp: 2025-01-02}</t>
+  </si>
+  <si>
+    <t>reviews</t>
+  </si>
+  <si>
+    <t>{game: cod 4, text: good game, rating: 4}</t>
+  </si>
+  <si>
+    <t>ben@db.com</t>
+  </si>
+  <si>
+    <t>Ben</t>
+  </si>
+  <si>
+    <t>neb</t>
+  </si>
+  <si>
+    <t>{cod 4, true, shooter, windows only, infinity ward, 2009}</t>
+  </si>
+  <si>
+    <t>brians@db.com
+jame@db.com
+bob@db.com
+gavin@db.com</t>
+  </si>
+  <si>
+    <t>{chat: 1, message: "go away", timestamp: 2025-01-01}</t>
   </si>
 </sst>
 </file>
@@ -722,7 +952,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
@@ -814,44 +1044,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -894,52 +1090,99 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1391,76 +1634,76 @@
       <c r="B13" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="35" t="s">
+      <c r="C13" s="70" t="s">
         <v>24</v>
       </c>
-      <c r="D13" s="35"/>
-      <c r="E13" s="35"/>
-      <c r="F13" s="35"/>
-      <c r="G13" s="35"/>
-      <c r="H13" s="35"/>
-      <c r="I13" s="35"/>
-      <c r="J13" s="35"/>
-      <c r="K13" s="35"/>
-      <c r="L13" s="35"/>
-      <c r="M13" s="35"/>
-      <c r="N13" s="35"/>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70"/>
+      <c r="F13" s="70"/>
+      <c r="G13" s="70"/>
+      <c r="H13" s="70"/>
+      <c r="I13" s="70"/>
+      <c r="J13" s="70"/>
+      <c r="K13" s="70"/>
+      <c r="L13" s="70"/>
+      <c r="M13" s="70"/>
+      <c r="N13" s="70"/>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B14" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="33" t="s">
+      <c r="C14" s="68" t="s">
         <v>26</v>
       </c>
-      <c r="D14" s="34"/>
-      <c r="E14" s="34"/>
-      <c r="F14" s="34"/>
-      <c r="G14" s="34"/>
-      <c r="H14" s="34"/>
-      <c r="I14" s="34"/>
-      <c r="J14" s="34"/>
-      <c r="K14" s="34"/>
-      <c r="L14" s="34"/>
-      <c r="M14" s="34"/>
+      <c r="D14" s="69"/>
+      <c r="E14" s="69"/>
+      <c r="F14" s="69"/>
+      <c r="G14" s="69"/>
+      <c r="H14" s="69"/>
+      <c r="I14" s="69"/>
+      <c r="J14" s="69"/>
+      <c r="K14" s="69"/>
+      <c r="L14" s="69"/>
+      <c r="M14" s="69"/>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="34" t="s">
+      <c r="C15" s="69" t="s">
         <v>30</v>
       </c>
-      <c r="D15" s="34"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="34"/>
-      <c r="G15" s="34"/>
-      <c r="H15" s="34"/>
-      <c r="I15" s="34"/>
-      <c r="J15" s="34"/>
-      <c r="K15" s="34"/>
-      <c r="L15" s="34"/>
-      <c r="M15" s="34"/>
-      <c r="N15" s="34"/>
+      <c r="D15" s="69"/>
+      <c r="E15" s="69"/>
+      <c r="F15" s="69"/>
+      <c r="G15" s="69"/>
+      <c r="H15" s="69"/>
+      <c r="I15" s="69"/>
+      <c r="J15" s="69"/>
+      <c r="K15" s="69"/>
+      <c r="L15" s="69"/>
+      <c r="M15" s="69"/>
+      <c r="N15" s="69"/>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="34" t="s">
+      <c r="C16" s="69" t="s">
         <v>32</v>
       </c>
-      <c r="D16" s="34"/>
-      <c r="E16" s="34"/>
-      <c r="F16" s="34"/>
-      <c r="G16" s="34"/>
-      <c r="H16" s="34"/>
-      <c r="I16" s="34"/>
-      <c r="J16" s="34"/>
-      <c r="K16" s="34"/>
-      <c r="L16" s="34"/>
-      <c r="M16" s="34"/>
-      <c r="N16" s="34"/>
+      <c r="D16" s="69"/>
+      <c r="E16" s="69"/>
+      <c r="F16" s="69"/>
+      <c r="G16" s="69"/>
+      <c r="H16" s="69"/>
+      <c r="I16" s="69"/>
+      <c r="J16" s="69"/>
+      <c r="K16" s="69"/>
+      <c r="L16" s="69"/>
+      <c r="M16" s="69"/>
+      <c r="N16" s="69"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1495,20 +1738,20 @@
       </c>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B6" s="41" t="s">
+      <c r="B6" s="76" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="42"/>
-      <c r="D6" s="42"/>
-      <c r="E6" s="42"/>
-      <c r="F6" s="42"/>
-      <c r="G6" s="43"/>
-      <c r="I6" s="41" t="s">
+      <c r="C6" s="77"/>
+      <c r="D6" s="77"/>
+      <c r="E6" s="77"/>
+      <c r="F6" s="77"/>
+      <c r="G6" s="78"/>
+      <c r="I6" s="76" t="s">
         <v>56</v>
       </c>
-      <c r="J6" s="42"/>
-      <c r="K6" s="42"/>
-      <c r="L6" s="43"/>
+      <c r="J6" s="77"/>
+      <c r="K6" s="77"/>
+      <c r="L6" s="78"/>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B7" s="23" t="s">
@@ -1583,24 +1826,24 @@
       <c r="G9" s="13"/>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B10" s="41" t="s">
+      <c r="B10" s="76" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="43"/>
-      <c r="E10" s="41" t="s">
+      <c r="C10" s="78"/>
+      <c r="E10" s="76" t="s">
         <v>42</v>
       </c>
-      <c r="F10" s="43"/>
-      <c r="H10" s="41" t="s">
+      <c r="F10" s="78"/>
+      <c r="H10" s="76" t="s">
         <v>45</v>
       </c>
-      <c r="I10" s="43"/>
-      <c r="K10" s="36" t="s">
+      <c r="I10" s="78"/>
+      <c r="K10" s="71" t="s">
         <v>46</v>
       </c>
-      <c r="L10" s="37"/>
-      <c r="M10" s="37"/>
-      <c r="N10" s="38"/>
+      <c r="L10" s="72"/>
+      <c r="M10" s="72"/>
+      <c r="N10" s="73"/>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B11" s="20" t="s">
@@ -1705,20 +1948,20 @@
       <c r="F14" s="19"/>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B16" s="36" t="s">
+      <c r="B16" s="71" t="s">
         <v>50</v>
       </c>
-      <c r="C16" s="37"/>
-      <c r="D16" s="37"/>
-      <c r="E16" s="38"/>
-      <c r="G16" s="39" t="s">
+      <c r="C16" s="72"/>
+      <c r="D16" s="72"/>
+      <c r="E16" s="73"/>
+      <c r="G16" s="74" t="s">
         <v>55</v>
       </c>
-      <c r="H16" s="40"/>
-      <c r="J16" s="36" t="s">
+      <c r="H16" s="75"/>
+      <c r="J16" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="K16" s="38"/>
+      <c r="K16" s="73"/>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B17" s="23" t="s">
@@ -1904,104 +2147,104 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B2" s="56" t="s">
+      <c r="B2" s="45" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="57" t="s">
+      <c r="C2" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="57" t="s">
+      <c r="D2" s="46" t="s">
         <v>73</v>
       </c>
-      <c r="E2" s="57" t="s">
+      <c r="E2" s="46" t="s">
         <v>38</v>
       </c>
-      <c r="F2" s="57" t="s">
+      <c r="F2" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="57" t="s">
+      <c r="G2" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="57" t="s">
+      <c r="H2" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="57" t="s">
+      <c r="I2" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="57" t="s">
+      <c r="J2" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="57" t="s">
+      <c r="K2" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="57" t="s">
+      <c r="L2" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="57" t="s">
+      <c r="M2" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="N2" s="58" t="s">
+      <c r="N2" s="47" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B3" s="45"/>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="46"/>
-      <c r="H3" s="46"/>
-      <c r="I3" s="46"/>
-      <c r="J3" s="46"/>
-      <c r="K3" s="46"/>
-      <c r="L3" s="46"/>
-      <c r="M3" s="46"/>
-      <c r="N3" s="47"/>
+      <c r="B3" s="35"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="36"/>
     </row>
     <row r="4" spans="2:14" ht="119" x14ac:dyDescent="0.2">
-      <c r="B4" s="48">
-        <v>1</v>
-      </c>
-      <c r="C4" s="49" t="s">
+      <c r="B4" s="37">
+        <v>1</v>
+      </c>
+      <c r="C4" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="49" t="s">
+      <c r="D4" s="38" t="s">
         <v>73</v>
       </c>
-      <c r="E4" s="50" t="s">
+      <c r="E4" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="50" t="s">
+      <c r="F4" s="39" t="s">
         <v>74</v>
       </c>
-      <c r="G4" s="51" t="s">
+      <c r="G4" s="40" t="s">
         <v>75</v>
       </c>
-      <c r="H4" s="51" t="s">
+      <c r="H4" s="40" t="s">
         <v>76</v>
       </c>
-      <c r="I4" s="51" t="s">
+      <c r="I4" s="40" t="s">
         <v>77</v>
       </c>
-      <c r="J4" s="49" t="b">
+      <c r="J4" s="38" t="b">
         <v>0</v>
       </c>
-      <c r="K4" s="51" t="s">
+      <c r="K4" s="40" t="s">
         <v>78</v>
       </c>
-      <c r="L4" s="51" t="s">
+      <c r="L4" s="40" t="s">
         <v>80</v>
       </c>
-      <c r="M4" s="51" t="s">
+      <c r="M4" s="40" t="s">
         <v>79</v>
       </c>
-      <c r="N4" s="52" t="s">
+      <c r="N4" s="41" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B8" s="44"/>
+      <c r="B8" s="34"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -2027,79 +2270,85 @@
     <col min="9" max="9" width="10.5" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="16.6640625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="7.83203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.5" customWidth="1"/>
-    <col min="14" max="14" width="10.83203125" customWidth="1"/>
+    <col min="12" max="12" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="8.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
         <v>82</v>
       </c>
-      <c r="J3" s="61" t="s">
+      <c r="J3" s="10" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B5" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" s="54" t="s">
+      <c r="B5" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="D5" s="54" t="s">
+      <c r="D5" s="43" t="s">
         <v>38</v>
       </c>
-      <c r="E5" s="54" t="s">
+      <c r="E5" s="43" t="s">
         <v>73</v>
       </c>
-      <c r="F5" s="54" t="s">
+      <c r="F5" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="55" t="s">
+      <c r="G5" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="64" t="s">
+      <c r="J5" s="42" t="s">
         <v>148</v>
       </c>
-      <c r="K5" s="65" t="s">
+      <c r="K5" s="43" t="s">
         <v>52</v>
       </c>
-      <c r="L5" s="65" t="s">
+      <c r="L5" s="43" t="s">
         <v>49</v>
       </c>
-      <c r="M5" s="66" t="s">
+      <c r="M5" s="44" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B6" s="48">
-        <v>1</v>
-      </c>
-      <c r="C6" s="49" t="s">
+      <c r="B6" s="37">
+        <v>1</v>
+      </c>
+      <c r="C6" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="50" t="s">
+      <c r="D6" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="49" t="s">
+      <c r="E6" s="38" t="s">
         <v>73</v>
       </c>
-      <c r="F6" s="50" t="s">
+      <c r="F6" s="39" t="s">
         <v>74</v>
       </c>
-      <c r="G6" s="52" t="b">
+      <c r="G6" s="41" t="b">
         <v>0</v>
       </c>
-      <c r="J6" s="48">
-        <v>1</v>
-      </c>
-      <c r="K6" s="49">
+      <c r="J6" s="37">
+        <v>1</v>
+      </c>
+      <c r="K6" s="38">
         <v>5000</v>
       </c>
-      <c r="L6" s="49" t="s">
+      <c r="L6" s="38" t="s">
         <v>72</v>
       </c>
-      <c r="M6" s="52">
+      <c r="M6" s="41">
         <v>2</v>
       </c>
     </row>
@@ -2110,72 +2359,102 @@
       <c r="F9" t="s">
         <v>88</v>
       </c>
+      <c r="J9" t="s">
+        <v>155</v>
+      </c>
     </row>
     <row r="11" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B11" s="53" t="s">
+      <c r="B11" s="42" t="s">
         <v>86</v>
       </c>
-      <c r="C11" s="54" t="s">
+      <c r="C11" s="43" t="s">
         <v>87</v>
       </c>
-      <c r="D11" s="55" t="s">
+      <c r="D11" s="44" t="s">
         <v>85</v>
       </c>
-      <c r="F11" s="64" t="s">
+      <c r="F11" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="G11" s="65" t="s">
+      <c r="G11" s="43" t="s">
         <v>44</v>
       </c>
-      <c r="H11" s="66" t="s">
+      <c r="H11" s="44" t="s">
         <v>89</v>
       </c>
+      <c r="J11" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="K11" s="43" t="s">
+        <v>43</v>
+      </c>
+      <c r="L11" s="44" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="12" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B12" s="45">
-        <v>1</v>
-      </c>
-      <c r="C12" s="46">
+      <c r="B12" s="35">
+        <v>1</v>
+      </c>
+      <c r="C12" s="10">
         <v>2</v>
       </c>
-      <c r="D12" s="59">
+      <c r="D12" s="48">
         <v>45717</v>
       </c>
-      <c r="F12" s="45">
+      <c r="F12" s="35">
         <v>200</v>
       </c>
-      <c r="G12" s="46" t="s">
+      <c r="G12" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="H12" s="62" t="s">
+      <c r="H12" s="50" t="s">
         <v>91</v>
       </c>
+      <c r="J12" s="35">
+        <v>1</v>
+      </c>
+      <c r="K12" s="10">
+        <v>200</v>
+      </c>
+      <c r="L12" s="36" t="s">
+        <v>157</v>
+      </c>
     </row>
     <row r="13" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B13" s="48">
+      <c r="B13" s="37">
         <v>3</v>
       </c>
-      <c r="C13" s="49">
+      <c r="C13" s="38">
         <v>4</v>
       </c>
-      <c r="D13" s="60">
+      <c r="D13" s="49">
         <v>45716</v>
       </c>
-      <c r="F13" s="48">
+      <c r="F13" s="37">
         <v>201</v>
       </c>
-      <c r="G13" s="49" t="s">
+      <c r="G13" s="38" t="s">
         <v>92</v>
       </c>
-      <c r="H13" s="63" t="s">
+      <c r="H13" s="51" t="s">
         <v>91</v>
+      </c>
+      <c r="J13" s="37">
+        <v>2</v>
+      </c>
+      <c r="K13" s="38">
+        <v>200</v>
+      </c>
+      <c r="L13" s="41" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="16" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
         <v>93</v>
       </c>
-      <c r="G16" s="61" t="s">
+      <c r="G16" s="10" t="s">
         <v>97</v>
       </c>
       <c r="L16" t="s">
@@ -2183,179 +2462,179 @@
       </c>
     </row>
     <row r="18" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B18" s="53" t="s">
+      <c r="B18" s="42" t="s">
         <v>47</v>
       </c>
-      <c r="C18" s="54" t="s">
+      <c r="C18" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="D18" s="54" t="s">
+      <c r="D18" s="43" t="s">
         <v>94</v>
       </c>
-      <c r="E18" s="55" t="s">
+      <c r="E18" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="G18" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="H18" s="65" t="s">
+      <c r="G18" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="H18" s="43" t="s">
         <v>52</v>
       </c>
-      <c r="I18" s="65" t="s">
+      <c r="I18" s="43" t="s">
         <v>98</v>
       </c>
-      <c r="J18" s="66" t="s">
+      <c r="J18" s="44" t="s">
         <v>99</v>
       </c>
-      <c r="L18" s="64" t="s">
+      <c r="L18" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="M18" s="65" t="s">
+      <c r="M18" s="43" t="s">
         <v>126</v>
       </c>
-      <c r="N18" s="65" t="s">
+      <c r="N18" s="43" t="s">
         <v>127</v>
       </c>
-      <c r="O18" s="65" t="s">
+      <c r="O18" s="43" t="s">
         <v>128</v>
       </c>
-      <c r="P18" s="65" t="s">
+      <c r="P18" s="43" t="s">
         <v>129</v>
       </c>
-      <c r="Q18" s="65" t="s">
+      <c r="Q18" s="43" t="s">
         <v>130</v>
       </c>
-      <c r="R18" s="65" t="s">
+      <c r="R18" s="43" t="s">
         <v>131</v>
       </c>
-      <c r="S18" s="65" t="s">
+      <c r="S18" s="43" t="s">
         <v>132</v>
       </c>
-      <c r="T18" s="65" t="s">
+      <c r="T18" s="43" t="s">
         <v>133</v>
       </c>
-      <c r="U18" s="65" t="s">
+      <c r="U18" s="43" t="s">
         <v>134</v>
       </c>
-      <c r="V18" s="66" t="s">
+      <c r="V18" s="44" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="19" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B19" s="45">
+      <c r="B19" s="35">
         <v>2000</v>
       </c>
-      <c r="C19" s="46">
+      <c r="C19" s="10">
         <v>200</v>
       </c>
-      <c r="D19" s="46">
-        <v>1</v>
-      </c>
-      <c r="E19" s="47" t="s">
+      <c r="D19" s="10">
+        <v>1</v>
+      </c>
+      <c r="E19" s="36" t="s">
         <v>95</v>
       </c>
-      <c r="G19" s="67">
-        <v>1</v>
-      </c>
-      <c r="H19" s="61">
+      <c r="G19" s="35">
+        <v>1</v>
+      </c>
+      <c r="H19" s="10">
         <v>5000</v>
       </c>
-      <c r="I19" s="68">
+      <c r="I19" s="52">
         <v>45748</v>
       </c>
-      <c r="J19" s="47" t="s">
+      <c r="J19" s="36" t="s">
         <v>100</v>
       </c>
-      <c r="L19" s="67">
+      <c r="L19" s="35">
         <v>12000</v>
       </c>
-      <c r="M19" s="46" t="b">
+      <c r="M19" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="N19" s="46" t="b">
-        <v>1</v>
-      </c>
-      <c r="O19" s="46" t="b">
+      <c r="N19" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="O19" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="P19" s="46" t="s">
+      <c r="P19" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="Q19" s="46" t="s">
+      <c r="Q19" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="R19" s="46" t="s">
+      <c r="R19" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="S19" s="46" t="s">
+      <c r="S19" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="T19" s="46" t="s">
+      <c r="T19" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="U19" s="46" t="s">
+      <c r="U19" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="V19" s="47" t="s">
+      <c r="V19" s="36" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="20" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B20" s="48">
+      <c r="B20" s="37">
         <v>2003</v>
       </c>
-      <c r="C20" s="49">
+      <c r="C20" s="38">
         <v>200</v>
       </c>
-      <c r="D20" s="49">
+      <c r="D20" s="38">
         <v>2</v>
       </c>
-      <c r="E20" s="52" t="s">
+      <c r="E20" s="41" t="s">
         <v>96</v>
       </c>
-      <c r="G20" s="69">
-        <v>1</v>
-      </c>
-      <c r="H20" s="49">
+      <c r="G20" s="37">
+        <v>1</v>
+      </c>
+      <c r="H20" s="38">
         <v>5001</v>
       </c>
-      <c r="I20" s="70">
+      <c r="I20" s="53">
         <v>2958352</v>
       </c>
-      <c r="J20" s="52" t="s">
+      <c r="J20" s="41" t="s">
         <v>101</v>
       </c>
-      <c r="L20" s="69">
+      <c r="L20" s="37">
         <v>12111</v>
       </c>
-      <c r="M20" s="49" t="b">
-        <v>1</v>
-      </c>
-      <c r="N20" s="49" t="b">
-        <v>1</v>
-      </c>
-      <c r="O20" s="49" t="b">
-        <v>1</v>
-      </c>
-      <c r="P20" s="49" t="s">
+      <c r="M20" s="38" t="b">
+        <v>1</v>
+      </c>
+      <c r="N20" s="38" t="b">
+        <v>1</v>
+      </c>
+      <c r="O20" s="38" t="b">
+        <v>1</v>
+      </c>
+      <c r="P20" s="38" t="s">
         <v>143</v>
       </c>
-      <c r="Q20" s="49" t="s">
+      <c r="Q20" s="38" t="s">
         <v>144</v>
       </c>
-      <c r="R20" s="49" t="s">
+      <c r="R20" s="38" t="s">
         <v>138</v>
       </c>
-      <c r="S20" s="49" t="s">
+      <c r="S20" s="38" t="s">
         <v>139</v>
       </c>
-      <c r="T20" s="49" t="s">
+      <c r="T20" s="38" t="s">
         <v>141</v>
       </c>
-      <c r="U20" s="49" t="s">
+      <c r="U20" s="38" t="s">
         <v>145</v>
       </c>
-      <c r="V20" s="52" t="s">
+      <c r="V20" s="41" t="s">
         <v>146</v>
       </c>
     </row>
@@ -2363,7 +2642,7 @@
       <c r="B23" t="s">
         <v>102</v>
       </c>
-      <c r="J23" s="61" t="s">
+      <c r="J23" s="10" t="s">
         <v>123</v>
       </c>
     </row>
@@ -2377,227 +2656,227 @@
       <c r="H24" s="10"/>
     </row>
     <row r="25" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B25" s="53" t="s">
+      <c r="B25" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="C25" s="54" t="s">
+      <c r="C25" s="43" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="54" t="s">
+      <c r="D25" s="43" t="s">
         <v>53</v>
       </c>
-      <c r="E25" s="54" t="s">
+      <c r="E25" s="43" t="s">
         <v>54</v>
       </c>
-      <c r="F25" s="54" t="s">
+      <c r="F25" s="43" t="s">
         <v>103</v>
       </c>
-      <c r="G25" s="54" t="s">
+      <c r="G25" s="43" t="s">
         <v>104</v>
       </c>
-      <c r="H25" s="55" t="s">
+      <c r="H25" s="44" t="s">
         <v>105</v>
       </c>
-      <c r="J25" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="K25" s="65" t="s">
+      <c r="J25" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="K25" s="43" t="s">
         <v>52</v>
       </c>
-      <c r="L25" s="66" t="s">
-        <v>124</v>
-      </c>
-      <c r="N25" s="61"/>
+      <c r="L25" s="44" t="s">
+        <v>159</v>
+      </c>
+      <c r="N25" s="10"/>
     </row>
     <row r="26" spans="2:22" ht="68" x14ac:dyDescent="0.2">
-      <c r="B26" s="45">
+      <c r="B26" s="35">
         <v>5000</v>
       </c>
-      <c r="C26" s="46" t="s">
+      <c r="C26" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="D26" s="71" t="s">
+      <c r="D26" s="33" t="s">
         <v>111</v>
       </c>
-      <c r="E26" s="46" t="b">
-        <v>1</v>
-      </c>
-      <c r="F26" s="46">
+      <c r="E26" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="F26" s="10">
         <v>12000</v>
       </c>
-      <c r="G26" s="46" t="s">
+      <c r="G26" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="H26" s="59">
+      <c r="H26" s="48">
         <v>39391</v>
       </c>
-      <c r="J26" s="72">
-        <v>1</v>
-      </c>
-      <c r="K26" s="46">
+      <c r="J26" s="54">
+        <v>1</v>
+      </c>
+      <c r="K26" s="10">
         <v>5000</v>
       </c>
-      <c r="L26" s="59">
+      <c r="L26" s="48">
         <v>45658</v>
       </c>
     </row>
     <row r="27" spans="2:22" ht="34" x14ac:dyDescent="0.2">
-      <c r="B27" s="45">
+      <c r="B27" s="35">
         <v>5001</v>
       </c>
-      <c r="C27" s="46" t="s">
+      <c r="C27" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="D27" s="71" t="s">
+      <c r="D27" s="33" t="s">
         <v>112</v>
       </c>
-      <c r="E27" s="46" t="b">
-        <v>1</v>
-      </c>
-      <c r="F27" s="46">
+      <c r="E27" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="F27" s="10">
         <v>12111</v>
       </c>
-      <c r="G27" s="46" t="s">
+      <c r="G27" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="H27" s="59">
+      <c r="H27" s="48">
         <v>44047</v>
       </c>
-      <c r="J27" s="72">
-        <v>1</v>
-      </c>
-      <c r="K27" s="46">
+      <c r="J27" s="54">
+        <v>1</v>
+      </c>
+      <c r="K27" s="10">
         <v>5001</v>
       </c>
-      <c r="L27" s="59">
+      <c r="L27" s="48">
         <v>45658</v>
       </c>
     </row>
     <row r="28" spans="2:22" ht="51" x14ac:dyDescent="0.2">
-      <c r="B28" s="45">
+      <c r="B28" s="35">
         <v>5002</v>
       </c>
-      <c r="C28" s="46" t="s">
+      <c r="C28" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="D28" s="71" t="s">
+      <c r="D28" s="33" t="s">
         <v>113</v>
       </c>
-      <c r="E28" s="46" t="b">
-        <v>1</v>
-      </c>
-      <c r="F28" s="46">
+      <c r="E28" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="F28" s="10">
         <v>12222</v>
       </c>
-      <c r="G28" s="46" t="s">
+      <c r="G28" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="H28" s="59">
+      <c r="H28" s="48">
         <v>39567</v>
       </c>
-      <c r="J28" s="72">
-        <v>1</v>
-      </c>
-      <c r="K28" s="46">
+      <c r="J28" s="54">
+        <v>1</v>
+      </c>
+      <c r="K28" s="10">
         <v>5002</v>
       </c>
-      <c r="L28" s="59">
+      <c r="L28" s="48">
         <v>45658</v>
       </c>
     </row>
     <row r="29" spans="2:22" ht="68" x14ac:dyDescent="0.2">
-      <c r="B29" s="45">
+      <c r="B29" s="35">
         <v>5003</v>
       </c>
-      <c r="C29" s="46" t="s">
+      <c r="C29" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="D29" s="71" t="s">
+      <c r="D29" s="33" t="s">
         <v>114</v>
       </c>
-      <c r="E29" s="46" t="b">
-        <v>1</v>
-      </c>
-      <c r="F29" s="46">
+      <c r="E29" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="F29" s="10">
         <v>12333</v>
       </c>
-      <c r="G29" s="46" t="s">
+      <c r="G29" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="H29" s="59">
+      <c r="H29" s="48">
         <v>41499</v>
       </c>
-      <c r="J29" s="72">
-        <v>1</v>
-      </c>
-      <c r="K29" s="46">
+      <c r="J29" s="54">
+        <v>1</v>
+      </c>
+      <c r="K29" s="10">
         <v>5003</v>
       </c>
-      <c r="L29" s="59">
+      <c r="L29" s="48">
         <v>45658</v>
       </c>
     </row>
     <row r="30" spans="2:22" ht="17" x14ac:dyDescent="0.2">
-      <c r="B30" s="45">
+      <c r="B30" s="35">
         <v>5004</v>
       </c>
-      <c r="C30" s="46" t="s">
+      <c r="C30" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="D30" s="71" t="s">
+      <c r="D30" s="33" t="s">
         <v>115</v>
       </c>
-      <c r="E30" s="46" t="b">
+      <c r="E30" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="F30" s="46">
+      <c r="F30" s="10">
         <v>12444</v>
       </c>
-      <c r="G30" s="46" t="s">
+      <c r="G30" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="H30" s="59">
+      <c r="H30" s="48">
         <v>29363</v>
       </c>
-      <c r="J30" s="72">
-        <v>1</v>
-      </c>
-      <c r="K30" s="46">
+      <c r="J30" s="54">
+        <v>1</v>
+      </c>
+      <c r="K30" s="10">
         <v>5004</v>
       </c>
-      <c r="L30" s="59">
+      <c r="L30" s="48">
         <v>45658</v>
       </c>
     </row>
     <row r="31" spans="2:22" ht="51" x14ac:dyDescent="0.2">
-      <c r="B31" s="48">
+      <c r="B31" s="37">
         <v>5005</v>
       </c>
-      <c r="C31" s="49" t="s">
+      <c r="C31" s="38" t="s">
         <v>110</v>
       </c>
-      <c r="D31" s="51" t="s">
+      <c r="D31" s="40" t="s">
         <v>116</v>
       </c>
-      <c r="E31" s="49" t="b">
+      <c r="E31" s="38" t="b">
         <v>0</v>
       </c>
-      <c r="F31" s="49">
+      <c r="F31" s="38">
         <v>12555</v>
       </c>
-      <c r="G31" s="49" t="s">
+      <c r="G31" s="38" t="s">
         <v>122</v>
       </c>
-      <c r="H31" s="60">
+      <c r="H31" s="49">
         <v>41730</v>
       </c>
-      <c r="J31" s="73">
-        <v>1</v>
-      </c>
-      <c r="K31" s="49">
+      <c r="J31" s="55">
+        <v>1</v>
+      </c>
+      <c r="K31" s="38">
         <v>5005</v>
       </c>
-      <c r="L31" s="60">
+      <c r="L31" s="49">
         <v>45658</v>
       </c>
     </row>
@@ -2625,92 +2904,94 @@
     <col min="7" max="7" width="17.5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="20.5" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="7.83203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.83203125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="13.83203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.1640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.83203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="6" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="8.33203125" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="7.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
         <v>82</v>
       </c>
-      <c r="J3" s="61" t="s">
+      <c r="J3" s="10" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B5" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" s="54" t="s">
+    <row r="5" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B5" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="D5" s="54" t="s">
+      <c r="D5" s="43" t="s">
         <v>38</v>
       </c>
-      <c r="E5" s="54" t="s">
+      <c r="E5" s="43" t="s">
         <v>73</v>
       </c>
-      <c r="F5" s="54" t="s">
+      <c r="F5" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="55" t="s">
+      <c r="G5" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="64" t="s">
+      <c r="J5" s="42" t="s">
         <v>148</v>
       </c>
-      <c r="K5" s="65" t="s">
+      <c r="K5" s="43" t="s">
         <v>52</v>
       </c>
-      <c r="L5" s="65" t="s">
+      <c r="L5" s="43" t="s">
         <v>49</v>
       </c>
-      <c r="M5" s="66" t="s">
+      <c r="M5" s="44" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B6" s="48">
-        <v>1</v>
-      </c>
-      <c r="C6" s="49" t="s">
+    <row r="6" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B6" s="37">
+        <v>1</v>
+      </c>
+      <c r="C6" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="50" t="s">
+      <c r="D6" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="49" t="s">
+      <c r="E6" s="38" t="s">
         <v>73</v>
       </c>
-      <c r="F6" s="50" t="s">
+      <c r="F6" s="39" t="s">
         <v>74</v>
       </c>
-      <c r="G6" s="52" t="b">
+      <c r="G6" s="41" t="b">
         <v>0</v>
       </c>
-      <c r="J6" s="48">
-        <v>1</v>
-      </c>
-      <c r="K6" s="49">
+      <c r="J6" s="37">
+        <v>1</v>
+      </c>
+      <c r="K6" s="38">
         <v>5000</v>
       </c>
-      <c r="L6" s="49" t="s">
+      <c r="L6" s="38" t="s">
         <v>72</v>
       </c>
-      <c r="M6" s="52">
+      <c r="M6" s="41">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
         <v>84</v>
       </c>
@@ -2718,93 +2999,161 @@
         <v>88</v>
       </c>
       <c r="J9" t="s">
+        <v>155</v>
+      </c>
+      <c r="N9" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B11" s="53" t="s">
+      <c r="Q9" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="11" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B11" s="42" t="s">
         <v>86</v>
       </c>
-      <c r="C11" s="54" t="s">
+      <c r="C11" s="43" t="s">
         <v>87</v>
       </c>
-      <c r="D11" s="55" t="s">
+      <c r="D11" s="44" t="s">
         <v>85</v>
       </c>
-      <c r="F11" s="64" t="s">
+      <c r="F11" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="G11" s="65" t="s">
+      <c r="G11" s="43" t="s">
         <v>44</v>
       </c>
-      <c r="H11" s="66" t="s">
+      <c r="H11" s="44" t="s">
         <v>89</v>
       </c>
-      <c r="J11" s="64" t="s">
+      <c r="J11" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="K11" s="43" t="s">
+        <v>43</v>
+      </c>
+      <c r="L11" s="44" t="s">
+        <v>156</v>
+      </c>
+      <c r="N11" s="42" t="s">
         <v>150</v>
       </c>
-      <c r="K11" s="66" t="s">
+      <c r="O11" s="44" t="s">
         <v>99</v>
       </c>
-      <c r="L11" s="61"/>
-    </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B12" s="45">
-        <v>1</v>
-      </c>
-      <c r="C12" s="46">
+      <c r="Q11" s="42" t="s">
+        <v>175</v>
+      </c>
+      <c r="R11" s="43" t="s">
+        <v>126</v>
+      </c>
+      <c r="S11" s="43" t="s">
+        <v>127</v>
+      </c>
+      <c r="T11" s="44" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="12" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B12" s="35">
+        <v>1</v>
+      </c>
+      <c r="C12" s="10">
         <v>2</v>
       </c>
-      <c r="D12" s="59">
+      <c r="D12" s="48">
         <v>45717</v>
       </c>
-      <c r="F12" s="45">
+      <c r="F12" s="35">
         <v>200</v>
       </c>
-      <c r="G12" s="46" t="s">
+      <c r="G12" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="H12" s="62" t="s">
+      <c r="H12" s="50" t="s">
         <v>91</v>
       </c>
-      <c r="J12" s="75" t="s">
+      <c r="J12" s="35">
+        <v>1</v>
+      </c>
+      <c r="K12" s="10">
+        <v>200</v>
+      </c>
+      <c r="L12" s="36" t="s">
+        <v>157</v>
+      </c>
+      <c r="N12" s="56" t="s">
         <v>151</v>
       </c>
-      <c r="K12" s="76" t="s">
+      <c r="O12" s="57" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B13" s="48">
+      <c r="Q12" s="35">
+        <v>12000</v>
+      </c>
+      <c r="R12" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="S12" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" s="36" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B13" s="37">
         <v>3</v>
       </c>
-      <c r="C13" s="49">
+      <c r="C13" s="38">
         <v>4</v>
       </c>
-      <c r="D13" s="60">
+      <c r="D13" s="49">
         <v>45716</v>
       </c>
-      <c r="F13" s="48">
+      <c r="F13" s="37">
         <v>201</v>
       </c>
-      <c r="G13" s="49" t="s">
+      <c r="G13" s="38" t="s">
         <v>92</v>
       </c>
-      <c r="H13" s="63" t="s">
+      <c r="H13" s="51" t="s">
         <v>91</v>
       </c>
-      <c r="J13" s="77" t="s">
+      <c r="J13" s="37">
+        <v>2</v>
+      </c>
+      <c r="K13" s="38">
+        <v>200</v>
+      </c>
+      <c r="L13" s="41" t="s">
+        <v>158</v>
+      </c>
+      <c r="N13" s="58" t="s">
         <v>152</v>
       </c>
-      <c r="K13" s="78" t="s">
+      <c r="O13" s="59" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="Q13" s="37">
+        <v>12111</v>
+      </c>
+      <c r="R13" s="38" t="b">
+        <v>1</v>
+      </c>
+      <c r="S13" s="38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" s="41" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
         <v>93</v>
       </c>
-      <c r="G16" s="61" t="s">
+      <c r="G16" s="10" t="s">
         <v>97</v>
       </c>
       <c r="L16" t="s">
@@ -2812,188 +3161,155 @@
       </c>
     </row>
     <row r="18" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B18" s="53" t="s">
+      <c r="B18" s="42" t="s">
         <v>47</v>
       </c>
-      <c r="C18" s="54" t="s">
+      <c r="C18" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="D18" s="54" t="s">
+      <c r="D18" s="43" t="s">
         <v>94</v>
       </c>
-      <c r="E18" s="55" t="s">
+      <c r="E18" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="G18" s="64" t="s">
+      <c r="G18" s="42" t="s">
         <v>150</v>
       </c>
-      <c r="H18" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="I18" s="65" t="s">
+      <c r="H18" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="I18" s="43" t="s">
         <v>52</v>
       </c>
-      <c r="J18" s="66" t="s">
+      <c r="J18" s="44" t="s">
         <v>98</v>
       </c>
-      <c r="L18" s="64" t="s">
-        <v>34</v>
-      </c>
-      <c r="M18" s="65" t="s">
-        <v>126</v>
-      </c>
-      <c r="N18" s="65" t="s">
-        <v>127</v>
-      </c>
-      <c r="O18" s="65" t="s">
-        <v>128</v>
-      </c>
-      <c r="P18" s="65" t="s">
-        <v>129</v>
-      </c>
-      <c r="Q18" s="65" t="s">
-        <v>130</v>
-      </c>
-      <c r="R18" s="65" t="s">
-        <v>131</v>
-      </c>
-      <c r="S18" s="65" t="s">
-        <v>132</v>
-      </c>
-      <c r="T18" s="65" t="s">
-        <v>133</v>
-      </c>
-      <c r="U18" s="65" t="s">
-        <v>134</v>
-      </c>
-      <c r="V18" s="66" t="s">
+      <c r="L18" s="42" t="s">
+        <v>175</v>
+      </c>
+      <c r="M18" s="43" t="s">
+        <v>176</v>
+      </c>
+      <c r="N18" s="43" t="s">
+        <v>177</v>
+      </c>
+      <c r="O18" s="43" t="s">
         <v>135</v>
       </c>
+      <c r="P18" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q18" s="10"/>
+      <c r="R18" s="10"/>
+      <c r="S18" s="10"/>
+      <c r="T18" s="10"/>
+      <c r="U18" s="10"/>
+      <c r="V18" s="10"/>
     </row>
     <row r="19" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B19" s="45">
+      <c r="B19" s="35">
         <v>2000</v>
       </c>
-      <c r="C19" s="46">
+      <c r="C19" s="10">
         <v>200</v>
       </c>
-      <c r="D19" s="46">
-        <v>1</v>
-      </c>
-      <c r="E19" s="47" t="s">
+      <c r="D19" s="10">
+        <v>1</v>
+      </c>
+      <c r="E19" s="36" t="s">
         <v>95</v>
       </c>
-      <c r="G19" s="75" t="s">
+      <c r="G19" s="56" t="s">
         <v>151</v>
       </c>
-      <c r="H19" s="61">
-        <v>1</v>
-      </c>
-      <c r="I19" s="61">
+      <c r="H19" s="10">
+        <v>1</v>
+      </c>
+      <c r="I19" s="10">
         <v>5000</v>
       </c>
-      <c r="J19" s="59">
+      <c r="J19" s="48">
         <v>45748</v>
       </c>
-      <c r="L19" s="67">
+      <c r="L19" s="35">
         <v>12000</v>
       </c>
-      <c r="M19" s="46" t="b">
+      <c r="M19" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="N19" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="O19" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="P19" s="36" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q19" s="10"/>
+      <c r="R19" s="10"/>
+      <c r="S19" s="10"/>
+      <c r="T19" s="10"/>
+      <c r="U19" s="10"/>
+      <c r="V19" s="10"/>
+    </row>
+    <row r="20" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B20" s="37">
+        <v>2003</v>
+      </c>
+      <c r="C20" s="38">
+        <v>200</v>
+      </c>
+      <c r="D20" s="38">
+        <v>2</v>
+      </c>
+      <c r="E20" s="41" t="s">
+        <v>96</v>
+      </c>
+      <c r="G20" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="H20" s="38">
+        <v>1</v>
+      </c>
+      <c r="I20" s="38">
+        <v>5001</v>
+      </c>
+      <c r="J20" s="49">
+        <v>2958352</v>
+      </c>
+      <c r="L20" s="37">
+        <v>12111</v>
+      </c>
+      <c r="M20" s="38" t="s">
+        <v>167</v>
+      </c>
+      <c r="N20" s="38" t="s">
+        <v>168</v>
+      </c>
+      <c r="O20" s="38" t="s">
+        <v>146</v>
+      </c>
+      <c r="P20" s="41" t="b">
         <v>0</v>
       </c>
-      <c r="N19" s="46" t="b">
-        <v>1</v>
-      </c>
-      <c r="O19" s="46" t="b">
-        <v>0</v>
-      </c>
-      <c r="P19" s="46" t="s">
-        <v>137</v>
-      </c>
-      <c r="Q19" s="46" t="s">
-        <v>136</v>
-      </c>
-      <c r="R19" s="46" t="s">
-        <v>138</v>
-      </c>
-      <c r="S19" s="46" t="s">
-        <v>139</v>
-      </c>
-      <c r="T19" s="46" t="s">
-        <v>140</v>
-      </c>
-      <c r="U19" s="46" t="s">
-        <v>141</v>
-      </c>
-      <c r="V19" s="47" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="20" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B20" s="48">
-        <v>2003</v>
-      </c>
-      <c r="C20" s="49">
-        <v>200</v>
-      </c>
-      <c r="D20" s="49">
-        <v>2</v>
-      </c>
-      <c r="E20" s="52" t="s">
-        <v>96</v>
-      </c>
-      <c r="G20" s="69" t="s">
-        <v>152</v>
-      </c>
-      <c r="H20" s="74">
-        <v>1</v>
-      </c>
-      <c r="I20" s="49">
-        <v>5001</v>
-      </c>
-      <c r="J20" s="60">
-        <v>2958352</v>
-      </c>
-      <c r="L20" s="69">
-        <v>12111</v>
-      </c>
-      <c r="M20" s="49" t="b">
-        <v>1</v>
-      </c>
-      <c r="N20" s="49" t="b">
-        <v>1</v>
-      </c>
-      <c r="O20" s="49" t="b">
-        <v>1</v>
-      </c>
-      <c r="P20" s="49" t="s">
-        <v>143</v>
-      </c>
-      <c r="Q20" s="49" t="s">
-        <v>144</v>
-      </c>
-      <c r="R20" s="49" t="s">
-        <v>138</v>
-      </c>
-      <c r="S20" s="49" t="s">
-        <v>139</v>
-      </c>
-      <c r="T20" s="49" t="s">
-        <v>141</v>
-      </c>
-      <c r="U20" s="49" t="s">
-        <v>145</v>
-      </c>
-      <c r="V20" s="52" t="s">
-        <v>146</v>
-      </c>
+      <c r="Q20" s="10"/>
+      <c r="R20" s="10"/>
+      <c r="S20" s="10"/>
+      <c r="T20" s="10"/>
+      <c r="U20" s="10"/>
+      <c r="V20" s="10"/>
     </row>
     <row r="23" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B23" t="s">
         <v>102</v>
       </c>
-      <c r="J23" s="61" t="s">
+      <c r="J23" s="10" t="s">
         <v>123</v>
+      </c>
+      <c r="N23" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="24" spans="2:22" x14ac:dyDescent="0.2">
@@ -3006,227 +3322,287 @@
       <c r="H24" s="10"/>
     </row>
     <row r="25" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B25" s="53" t="s">
+      <c r="B25" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="C25" s="54" t="s">
+      <c r="C25" s="43" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="54" t="s">
+      <c r="D25" s="43" t="s">
         <v>53</v>
       </c>
-      <c r="E25" s="54" t="s">
+      <c r="E25" s="43" t="s">
         <v>54</v>
       </c>
-      <c r="F25" s="54" t="s">
+      <c r="F25" s="43" t="s">
         <v>103</v>
       </c>
-      <c r="G25" s="54" t="s">
+      <c r="G25" s="43" t="s">
         <v>104</v>
       </c>
-      <c r="H25" s="55" t="s">
+      <c r="H25" s="44" t="s">
         <v>105</v>
       </c>
-      <c r="J25" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="K25" s="65" t="s">
+      <c r="J25" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="K25" s="43" t="s">
         <v>52</v>
       </c>
-      <c r="L25" s="66" t="s">
+      <c r="L25" s="44" t="s">
         <v>124</v>
       </c>
-      <c r="N25" s="61"/>
+      <c r="N25" s="62" t="s">
+        <v>161</v>
+      </c>
+      <c r="O25" s="60" t="s">
+        <v>162</v>
+      </c>
+      <c r="P25" s="60" t="s">
+        <v>163</v>
+      </c>
+      <c r="Q25" s="61" t="s">
+        <v>164</v>
+      </c>
+      <c r="R25" s="10"/>
     </row>
     <row r="26" spans="2:22" ht="68" x14ac:dyDescent="0.2">
-      <c r="B26" s="45">
+      <c r="B26" s="35">
         <v>5000</v>
       </c>
-      <c r="C26" s="46" t="s">
+      <c r="C26" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="D26" s="71" t="s">
+      <c r="D26" s="33" t="s">
         <v>111</v>
       </c>
-      <c r="E26" s="46" t="b">
-        <v>1</v>
-      </c>
-      <c r="F26" s="46">
+      <c r="E26" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="F26" s="10">
         <v>12000</v>
       </c>
-      <c r="G26" s="46" t="s">
+      <c r="G26" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="H26" s="59">
+      <c r="H26" s="48">
         <v>39391</v>
       </c>
-      <c r="J26" s="72">
-        <v>1</v>
-      </c>
-      <c r="K26" s="46">
+      <c r="J26" s="54">
+        <v>1</v>
+      </c>
+      <c r="K26" s="10">
         <v>5000</v>
       </c>
-      <c r="L26" s="59">
+      <c r="L26" s="48">
         <v>45658</v>
       </c>
+      <c r="N26" s="35" t="s">
+        <v>165</v>
+      </c>
+      <c r="O26" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="P26" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q26" s="36" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="27" spans="2:22" ht="34" x14ac:dyDescent="0.2">
-      <c r="B27" s="45">
+      <c r="B27" s="35">
         <v>5001</v>
       </c>
-      <c r="C27" s="46" t="s">
+      <c r="C27" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="D27" s="71" t="s">
+      <c r="D27" s="33" t="s">
         <v>112</v>
       </c>
-      <c r="E27" s="46" t="b">
-        <v>1</v>
-      </c>
-      <c r="F27" s="46">
+      <c r="E27" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="F27" s="10">
         <v>12111</v>
       </c>
-      <c r="G27" s="46" t="s">
+      <c r="G27" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="H27" s="59">
+      <c r="H27" s="48">
         <v>44047</v>
       </c>
-      <c r="J27" s="72">
-        <v>1</v>
-      </c>
-      <c r="K27" s="46">
+      <c r="J27" s="54">
+        <v>1</v>
+      </c>
+      <c r="K27" s="10">
         <v>5001</v>
       </c>
-      <c r="L27" s="59">
+      <c r="L27" s="48">
         <v>45658</v>
       </c>
+      <c r="N27" s="35" t="s">
+        <v>166</v>
+      </c>
+      <c r="O27" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="P27" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="Q27" s="36" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="28" spans="2:22" ht="51" x14ac:dyDescent="0.2">
-      <c r="B28" s="45">
+      <c r="B28" s="35">
         <v>5002</v>
       </c>
-      <c r="C28" s="46" t="s">
+      <c r="C28" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="D28" s="71" t="s">
+      <c r="D28" s="33" t="s">
         <v>113</v>
       </c>
-      <c r="E28" s="46" t="b">
-        <v>1</v>
-      </c>
-      <c r="F28" s="46">
+      <c r="E28" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="F28" s="10">
         <v>12222</v>
       </c>
-      <c r="G28" s="46" t="s">
+      <c r="G28" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="H28" s="59">
+      <c r="H28" s="48">
         <v>39567</v>
       </c>
-      <c r="J28" s="72">
-        <v>1</v>
-      </c>
-      <c r="K28" s="46">
+      <c r="J28" s="54">
+        <v>1</v>
+      </c>
+      <c r="K28" s="10">
         <v>5002</v>
       </c>
-      <c r="L28" s="59">
+      <c r="L28" s="48">
         <v>45658</v>
       </c>
+      <c r="N28" s="35" t="s">
+        <v>167</v>
+      </c>
+      <c r="O28" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="P28" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q28" s="36" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="29" spans="2:22" ht="68" x14ac:dyDescent="0.2">
-      <c r="B29" s="45">
+      <c r="B29" s="35">
         <v>5003</v>
       </c>
-      <c r="C29" s="46" t="s">
+      <c r="C29" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="D29" s="71" t="s">
+      <c r="D29" s="33" t="s">
         <v>114</v>
       </c>
-      <c r="E29" s="46" t="b">
-        <v>1</v>
-      </c>
-      <c r="F29" s="46">
+      <c r="E29" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="F29" s="10">
         <v>12333</v>
       </c>
-      <c r="G29" s="46" t="s">
+      <c r="G29" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="H29" s="59">
+      <c r="H29" s="48">
         <v>41499</v>
       </c>
-      <c r="J29" s="72">
-        <v>1</v>
-      </c>
-      <c r="K29" s="46">
+      <c r="J29" s="54">
+        <v>1</v>
+      </c>
+      <c r="K29" s="10">
         <v>5003</v>
       </c>
-      <c r="L29" s="59">
+      <c r="L29" s="48">
         <v>45658</v>
       </c>
+      <c r="N29" s="37" t="s">
+        <v>168</v>
+      </c>
+      <c r="O29" s="38" t="s">
+        <v>172</v>
+      </c>
+      <c r="P29" s="38" t="s">
+        <v>170</v>
+      </c>
+      <c r="Q29" s="41" t="s">
+        <v>145</v>
+      </c>
     </row>
     <row r="30" spans="2:22" ht="17" x14ac:dyDescent="0.2">
-      <c r="B30" s="45">
+      <c r="B30" s="35">
         <v>5004</v>
       </c>
-      <c r="C30" s="46" t="s">
+      <c r="C30" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="D30" s="71" t="s">
+      <c r="D30" s="33" t="s">
         <v>115</v>
       </c>
-      <c r="E30" s="46" t="b">
+      <c r="E30" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="F30" s="46">
+      <c r="F30" s="10">
         <v>12444</v>
       </c>
-      <c r="G30" s="46" t="s">
+      <c r="G30" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="H30" s="59">
+      <c r="H30" s="48">
         <v>29363</v>
       </c>
-      <c r="J30" s="72">
-        <v>1</v>
-      </c>
-      <c r="K30" s="46">
+      <c r="J30" s="54">
+        <v>1</v>
+      </c>
+      <c r="K30" s="10">
         <v>5004</v>
       </c>
-      <c r="L30" s="59">
+      <c r="L30" s="48">
         <v>45658</v>
       </c>
     </row>
     <row r="31" spans="2:22" ht="51" x14ac:dyDescent="0.2">
-      <c r="B31" s="48">
+      <c r="B31" s="37">
         <v>5005</v>
       </c>
-      <c r="C31" s="49" t="s">
+      <c r="C31" s="38" t="s">
         <v>110</v>
       </c>
-      <c r="D31" s="51" t="s">
+      <c r="D31" s="40" t="s">
         <v>116</v>
       </c>
-      <c r="E31" s="49" t="b">
+      <c r="E31" s="38" t="b">
         <v>0</v>
       </c>
-      <c r="F31" s="49">
+      <c r="F31" s="38">
         <v>12555</v>
       </c>
-      <c r="G31" s="49" t="s">
+      <c r="G31" s="38" t="s">
         <v>122</v>
       </c>
-      <c r="H31" s="60">
+      <c r="H31" s="49">
         <v>41730</v>
       </c>
-      <c r="J31" s="73">
-        <v>1</v>
-      </c>
-      <c r="K31" s="49">
+      <c r="J31" s="55">
+        <v>1</v>
+      </c>
+      <c r="K31" s="38">
         <v>5005</v>
       </c>
-      <c r="L31" s="60">
+      <c r="L31" s="49">
         <v>45658</v>
       </c>
     </row>
@@ -3239,4 +3615,468 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B26A5AB9-0351-8045-95A8-FDD6E42F5467}">
+  <dimension ref="B4:F54"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="30.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B4" t="s">
+        <v>190</v>
+      </c>
+      <c r="E4" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B6" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="C6" s="64" t="s">
+        <v>180</v>
+      </c>
+      <c r="E6" s="42" t="s">
+        <v>179</v>
+      </c>
+      <c r="F6" s="44" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="B7" s="65" t="s">
+        <v>181</v>
+      </c>
+      <c r="C7" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="E7" s="35" t="s">
+        <v>197</v>
+      </c>
+      <c r="F7" s="36" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="B8" s="65" t="s">
+        <v>184</v>
+      </c>
+      <c r="C8" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="E8" s="35" t="s">
+        <v>198</v>
+      </c>
+      <c r="F8" s="36" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="B9" s="65" t="s">
+        <v>185</v>
+      </c>
+      <c r="C9" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="E9" s="35" t="s">
+        <v>199</v>
+      </c>
+      <c r="F9" s="36" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" ht="34" x14ac:dyDescent="0.2">
+      <c r="B10" s="65" t="s">
+        <v>186</v>
+      </c>
+      <c r="C10" s="66" t="s">
+        <v>187</v>
+      </c>
+      <c r="E10" s="37" t="s">
+        <v>201</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" ht="34" x14ac:dyDescent="0.2">
+      <c r="B11" s="65" t="s">
+        <v>188</v>
+      </c>
+      <c r="C11" s="66" t="s">
+        <v>187</v>
+      </c>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+    </row>
+    <row r="12" spans="2:6" ht="85" x14ac:dyDescent="0.2">
+      <c r="B12" s="65" t="s">
+        <v>189</v>
+      </c>
+      <c r="C12" s="66" t="s">
+        <v>191</v>
+      </c>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10"/>
+    </row>
+    <row r="13" spans="2:6" ht="85" x14ac:dyDescent="0.2">
+      <c r="B13" s="65" t="s">
+        <v>192</v>
+      </c>
+      <c r="C13" s="66" t="s">
+        <v>193</v>
+      </c>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
+    </row>
+    <row r="14" spans="2:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="B14" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="C14" s="67" t="s">
+        <v>195</v>
+      </c>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10"/>
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B15" s="63"/>
+      <c r="C15" s="63"/>
+    </row>
+    <row r="16" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B16" s="63"/>
+      <c r="C16" s="63"/>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B17" s="63"/>
+      <c r="C17" s="63"/>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B18" s="63"/>
+      <c r="C18" s="63"/>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B19" s="63"/>
+      <c r="C19" s="63"/>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B20" s="63"/>
+      <c r="C20" s="63"/>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B21" s="63"/>
+      <c r="C21" s="63"/>
+    </row>
+    <row r="22" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B22" s="63"/>
+      <c r="C22" s="63"/>
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B23" s="63"/>
+      <c r="C23" s="63"/>
+    </row>
+    <row r="24" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B24" s="63"/>
+      <c r="C24" s="63"/>
+    </row>
+    <row r="25" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B25" s="63"/>
+      <c r="C25" s="63"/>
+    </row>
+    <row r="26" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B26" s="63"/>
+      <c r="C26" s="63"/>
+    </row>
+    <row r="27" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B27" s="63"/>
+      <c r="C27" s="63"/>
+    </row>
+    <row r="28" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B28" s="63"/>
+      <c r="C28" s="63"/>
+    </row>
+    <row r="29" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B29" s="63"/>
+      <c r="C29" s="63"/>
+    </row>
+    <row r="30" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B30" s="63"/>
+      <c r="C30" s="63"/>
+    </row>
+    <row r="31" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B31" s="63"/>
+      <c r="C31" s="63"/>
+    </row>
+    <row r="32" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B32" s="63"/>
+      <c r="C32" s="63"/>
+    </row>
+    <row r="33" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B33" s="63"/>
+      <c r="C33" s="63"/>
+    </row>
+    <row r="34" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B34" s="63"/>
+      <c r="C34" s="63"/>
+    </row>
+    <row r="35" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B35" s="63"/>
+      <c r="C35" s="63"/>
+    </row>
+    <row r="36" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B36" s="63"/>
+      <c r="C36" s="63"/>
+    </row>
+    <row r="37" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B37" s="63"/>
+      <c r="C37" s="63"/>
+    </row>
+    <row r="38" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B38" s="63"/>
+      <c r="C38" s="63"/>
+    </row>
+    <row r="39" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B39" s="63"/>
+      <c r="C39" s="63"/>
+    </row>
+    <row r="40" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B40" s="63"/>
+      <c r="C40" s="63"/>
+    </row>
+    <row r="41" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B41" s="63"/>
+      <c r="C41" s="63"/>
+    </row>
+    <row r="42" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B42" s="63"/>
+      <c r="C42" s="63"/>
+    </row>
+    <row r="43" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B43" s="63"/>
+      <c r="C43" s="63"/>
+    </row>
+    <row r="44" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B44" s="63"/>
+      <c r="C44" s="63"/>
+    </row>
+    <row r="45" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B45" s="63"/>
+      <c r="C45" s="63"/>
+    </row>
+    <row r="46" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B46" s="63"/>
+      <c r="C46" s="63"/>
+    </row>
+    <row r="47" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B47" s="63"/>
+      <c r="C47" s="63"/>
+    </row>
+    <row r="48" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B48" s="63"/>
+      <c r="C48" s="63"/>
+    </row>
+    <row r="49" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B49" s="63"/>
+      <c r="C49" s="63"/>
+    </row>
+    <row r="50" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B50" s="63"/>
+      <c r="C50" s="63"/>
+    </row>
+    <row r="51" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B51" s="63"/>
+      <c r="C51" s="63"/>
+    </row>
+    <row r="52" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B52" s="63"/>
+      <c r="C52" s="63"/>
+    </row>
+    <row r="53" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B53" s="63"/>
+      <c r="C53" s="63"/>
+    </row>
+    <row r="54" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B54" s="63"/>
+      <c r="C54" s="63"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA255782-6F17-8C4F-9575-C7BD905C6756}">
+  <dimension ref="B4:L11"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.83203125" customWidth="1"/>
+    <col min="8" max="8" width="48" customWidth="1"/>
+    <col min="9" max="9" width="14.5" customWidth="1"/>
+    <col min="11" max="11" width="43.6640625" customWidth="1"/>
+    <col min="12" max="12" width="33" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B4" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B6" s="10"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="10"/>
+      <c r="K6" s="10"/>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B7" s="42" t="s">
+        <v>204</v>
+      </c>
+      <c r="C7" s="43" t="s">
+        <v>83</v>
+      </c>
+      <c r="D7" s="43" t="s">
+        <v>73</v>
+      </c>
+      <c r="E7" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" s="43" t="s">
+        <v>9</v>
+      </c>
+      <c r="G7" s="43" t="s">
+        <v>51</v>
+      </c>
+      <c r="H7" s="43" t="s">
+        <v>207</v>
+      </c>
+      <c r="I7" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="J7" s="43" t="s">
+        <v>7</v>
+      </c>
+      <c r="K7" s="43" t="s">
+        <v>212</v>
+      </c>
+      <c r="L7" s="44" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="68" x14ac:dyDescent="0.2">
+      <c r="B8" s="83" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="81" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="81" t="s">
+        <v>205</v>
+      </c>
+      <c r="E8" s="80" t="s">
+        <v>206</v>
+      </c>
+      <c r="F8" s="81" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" s="82" t="s">
+        <v>209</v>
+      </c>
+      <c r="H8" s="82" t="s">
+        <v>208</v>
+      </c>
+      <c r="I8" s="82" t="s">
+        <v>210</v>
+      </c>
+      <c r="J8" s="82" t="s">
+        <v>211</v>
+      </c>
+      <c r="K8" s="82" t="s">
+        <v>213</v>
+      </c>
+      <c r="L8" s="36" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" ht="68" x14ac:dyDescent="0.2">
+      <c r="B9" s="79" t="s">
+        <v>216</v>
+      </c>
+      <c r="C9" s="38" t="s">
+        <v>217</v>
+      </c>
+      <c r="D9" s="38" t="s">
+        <v>218</v>
+      </c>
+      <c r="E9" s="39" t="s">
+        <v>206</v>
+      </c>
+      <c r="F9" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" s="38"/>
+      <c r="H9" s="38" t="s">
+        <v>219</v>
+      </c>
+      <c r="I9" s="40" t="s">
+        <v>220</v>
+      </c>
+      <c r="J9" s="38">
+        <v>1</v>
+      </c>
+      <c r="K9" s="38" t="s">
+        <v>221</v>
+      </c>
+      <c r="L9" s="59"/>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B10" s="10"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="10"/>
+      <c r="K10" s="10"/>
+    </row>
+    <row r="11" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="10"/>
+      <c r="J11" s="10"/>
+      <c r="K11" s="10"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B8" r:id="rId1" xr:uid="{AABFEEB2-6669-744C-BD96-63584FBB2DBC}"/>
+    <hyperlink ref="E8" r:id="rId2" xr:uid="{F931A007-CF50-CF46-84C5-C797F00B7F36}"/>
+    <hyperlink ref="B9" r:id="rId3" xr:uid="{28C4E258-2350-1B43-A372-21EFAFDA74B9}"/>
+    <hyperlink ref="E9" r:id="rId4" xr:uid="{7E9276DB-82FA-044B-83F3-3CE8DDDBC2B1}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>